--- a/files/upload/excel/20260817_ID-IBM_ID-_POU_Unreturned.xlsx
+++ b/files/upload/excel/20260817_ID-IBM_ID-_POU_Unreturned.xlsx
@@ -1,11 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30404"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="13" documentId="11_EB59AEE8F97DB29FF53E5B7B715A219348456A3E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{65052AF7-EA54-4E5D-A22B-AD59A7ED2A3B}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ibm-my.sharepoint.com/personal/miftah_choiri_ibm_com/Documents/IBM💼/PROJECTS🎯/OPPORTUNITY/LENOVO-REPORT/lenovo-apps/PoU unreturn/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="14" documentId="11_EB59AEE8F97DB29FF53E5B7B715A219348456A3E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3F185053-5CAD-455E-9FE6-8B4FA10BC232}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="120" windowWidth="18060" windowHeight="7050" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="4995" windowWidth="38700" windowHeight="15885" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -14,7 +19,7 @@
   </sheets>
   <calcPr calcId="191028"/>
   <pivotCaches>
-    <pivotCache cacheId="223" r:id="rId4"/>
+    <pivotCache cacheId="0" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -3766,7 +3771,7 @@
     <numFmt numFmtId="164" formatCode="[$-10409]0"/>
     <numFmt numFmtId="165" formatCode="[$-10409]dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -4019,7 +4024,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" readingOrder="1"/>
@@ -4081,9 +4086,20 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" pivotButton="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" pivotButton="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
@@ -4102,25 +4118,41 @@
     <xf numFmtId="0" fontId="1" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" pivotButton="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" pivotButton="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="34">
+    <dxf>
+      <alignment indent="0"/>
+    </dxf>
+    <dxf>
+      <alignment indent="0"/>
+    </dxf>
+    <dxf>
+      <alignment indent="0"/>
+    </dxf>
+    <dxf>
+      <alignment indent="0"/>
+    </dxf>
+    <dxf>
+      <alignment indent="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -4809,13 +4841,6 @@
     <dxf>
       <border>
         <bottom style="thin">
-          <color rgb="FF118DFF"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
           <color rgb="FFE5E5E5"/>
         </bottom>
       </border>
@@ -4845,6 +4870,13 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
     </dxf>
     <dxf>
+      <border>
+        <bottom style="thin">
+          <color rgb="FF118DFF"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <font>
         <b val="0"/>
         <i val="0"/>
@@ -4867,36 +4899,6 @@
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment indent="0"/>
-    </dxf>
-    <dxf>
-      <alignment indent="0"/>
-    </dxf>
-    <dxf>
-      <alignment indent="0"/>
-    </dxf>
-    <dxf>
-      <alignment indent="0"/>
-    </dxf>
-    <dxf>
-      <alignment indent="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -20404,7 +20406,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{983948A7-2C98-4C47-B385-659B2763C88B}" name="PivotTable1" cacheId="223" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{983948A7-2C98-4C47-B385-659B2763C88B}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:G8" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="20">
     <pivotField dataField="1" showAll="0"/>
@@ -20488,42 +20490,42 @@
     <dataField name="Count of SOID" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="10">
-    <format dxfId="24">
+    <format dxfId="9">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="25">
+    <format dxfId="8">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="26">
+    <format dxfId="7">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="27">
+    <format dxfId="6">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="28">
+    <format dxfId="5">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="29">
+    <format dxfId="4">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="30">
+    <format dxfId="3">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="31">
+    <format dxfId="2">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="32">
+    <format dxfId="1">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="33">
+    <format dxfId="0">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
@@ -20540,29 +20542,29 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2708165D-0E11-49D3-B0D2-62C1D1917EB9}" name="Table1" displayName="Table1" ref="A1:T698" totalsRowShown="0" headerRowDxfId="23" dataDxfId="22" headerRowBorderDxfId="20" tableBorderDxfId="21">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2708165D-0E11-49D3-B0D2-62C1D1917EB9}" name="Table1" displayName="Table1" ref="A1:T698" totalsRowShown="0" headerRowDxfId="33" dataDxfId="31" headerRowBorderDxfId="32" tableBorderDxfId="30">
   <autoFilter ref="A1:T698" xr:uid="{2708165D-0E11-49D3-B0D2-62C1D1917EB9}"/>
   <tableColumns count="20">
-    <tableColumn id="1" xr3:uid="{F9AC9A2A-DDAC-4EA7-8B32-3EAF709EBDD1}" name="SOID" dataDxfId="19"/>
-    <tableColumn id="2" xr3:uid="{F05C9500-D826-42DA-BBBC-8DF4B7987729}" name="Aging Days" dataDxfId="18"/>
-    <tableColumn id="3" xr3:uid="{1386FB3E-78EF-4BBD-A72D-A9BFB995B68C}" name="Aging Range" dataDxfId="17"/>
-    <tableColumn id="4" xr3:uid="{4474A62E-582C-4311-B0A0-A7D0081D913D}" name="Commodity Code" dataDxfId="16"/>
-    <tableColumn id="5" xr3:uid="{BC97C48C-CD23-4900-8F9D-BDFED4666E5E}" name="Ship PN" dataDxfId="15"/>
-    <tableColumn id="6" xr3:uid="{AB6D1CB5-1D6E-402E-9C40-09C0D260547B}" name="Vendor ID" dataDxfId="14"/>
-    <tableColumn id="7" xr3:uid="{C4B49B87-D1FA-419B-9817-7079BCE37A07}" name="Vendor Name" dataDxfId="13"/>
-    <tableColumn id="8" xr3:uid="{D916EA3D-DFDA-4297-A462-3D17D9AA2ED4}" name="Labor Status" dataDxfId="12"/>
-    <tableColumn id="9" xr3:uid="{E67F117C-D3E2-4D3A-9506-057E830ED2D7}" name="RMA Status" dataDxfId="11"/>
-    <tableColumn id="10" xr3:uid="{4E605F0E-8A85-43D3-A040-AA3D45EE0A4F}" name="Delivery Date" dataDxfId="10"/>
-    <tableColumn id="11" xr3:uid="{2342CB08-680C-4A09-ADD2-EDBC396EFB3E}" name="Labor Fixed Date" dataDxfId="9"/>
-    <tableColumn id="12" xr3:uid="{01B99FD9-75D3-40A4-A5ED-F006751EDCAD}" name="SO Completion Date" dataDxfId="8"/>
-    <tableColumn id="13" xr3:uid="{5675B07F-DF30-4183-9C54-46FB20D47078}" name="Return Date" dataDxfId="7"/>
-    <tableColumn id="14" xr3:uid="{69DA1764-D161-4D2D-87D7-6F51F3797FE2}" name="WO Type" dataDxfId="6"/>
-    <tableColumn id="15" xr3:uid="{C10487B9-7E60-4AD6-9617-CB505889A0A5}" name="Order Type" dataDxfId="5"/>
-    <tableColumn id="16" xr3:uid="{097C25DE-28C2-4AF8-818C-98F40FB8F143}" name="DC/Collection Form-Submitted Date" dataDxfId="4"/>
-    <tableColumn id="17" xr3:uid="{CB47269C-CB9B-485E-8208-D11B9F2F90FE}" name="DC/Collection Form" dataDxfId="3"/>
-    <tableColumn id="18" xr3:uid="{69BF9D96-667A-4BAC-8944-1FBA87756468}" name="AWB Number" dataDxfId="2"/>
-    <tableColumn id="19" xr3:uid="{BBE2F73B-F3A7-4B5C-9F2F-08A7F3712C23}" name="Return Status" dataDxfId="1"/>
-    <tableColumn id="20" xr3:uid="{D4DCAB7E-DDCB-4A54-8BC9-9D0BFB24894E}" name="Note" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{F9AC9A2A-DDAC-4EA7-8B32-3EAF709EBDD1}" name="SOID" dataDxfId="29"/>
+    <tableColumn id="2" xr3:uid="{F05C9500-D826-42DA-BBBC-8DF4B7987729}" name="Aging Days" dataDxfId="28"/>
+    <tableColumn id="3" xr3:uid="{1386FB3E-78EF-4BBD-A72D-A9BFB995B68C}" name="Aging Range" dataDxfId="27"/>
+    <tableColumn id="4" xr3:uid="{4474A62E-582C-4311-B0A0-A7D0081D913D}" name="Commodity Code" dataDxfId="26"/>
+    <tableColumn id="5" xr3:uid="{BC97C48C-CD23-4900-8F9D-BDFED4666E5E}" name="Ship PN" dataDxfId="25"/>
+    <tableColumn id="6" xr3:uid="{AB6D1CB5-1D6E-402E-9C40-09C0D260547B}" name="Vendor ID" dataDxfId="24"/>
+    <tableColumn id="7" xr3:uid="{C4B49B87-D1FA-419B-9817-7079BCE37A07}" name="Vendor Name" dataDxfId="23"/>
+    <tableColumn id="8" xr3:uid="{D916EA3D-DFDA-4297-A462-3D17D9AA2ED4}" name="Labor Status" dataDxfId="22"/>
+    <tableColumn id="9" xr3:uid="{E67F117C-D3E2-4D3A-9506-057E830ED2D7}" name="RMA Status" dataDxfId="21"/>
+    <tableColumn id="10" xr3:uid="{4E605F0E-8A85-43D3-A040-AA3D45EE0A4F}" name="Delivery Date" dataDxfId="20"/>
+    <tableColumn id="11" xr3:uid="{2342CB08-680C-4A09-ADD2-EDBC396EFB3E}" name="Labor Fixed Date" dataDxfId="19"/>
+    <tableColumn id="12" xr3:uid="{01B99FD9-75D3-40A4-A5ED-F006751EDCAD}" name="SO Completion Date" dataDxfId="18"/>
+    <tableColumn id="13" xr3:uid="{5675B07F-DF30-4183-9C54-46FB20D47078}" name="Return Date" dataDxfId="17"/>
+    <tableColumn id="14" xr3:uid="{69DA1764-D161-4D2D-87D7-6F51F3797FE2}" name="WO Type" dataDxfId="16"/>
+    <tableColumn id="15" xr3:uid="{C10487B9-7E60-4AD6-9617-CB505889A0A5}" name="Order Type" dataDxfId="15"/>
+    <tableColumn id="16" xr3:uid="{097C25DE-28C2-4AF8-818C-98F40FB8F143}" name="DC/Collection Form-Submitted Date" dataDxfId="14"/>
+    <tableColumn id="17" xr3:uid="{CB47269C-CB9B-485E-8208-D11B9F2F90FE}" name="DC/Collection Form" dataDxfId="13"/>
+    <tableColumn id="18" xr3:uid="{69BF9D96-667A-4BAC-8944-1FBA87756468}" name="AWB Number" dataDxfId="12"/>
+    <tableColumn id="19" xr3:uid="{BBE2F73B-F3A7-4B5C-9F2F-08A7F3712C23}" name="Return Status" dataDxfId="11"/>
+    <tableColumn id="20" xr3:uid="{D4DCAB7E-DDCB-4A54-8BC9-9D0BFB24894E}" name="Note" dataDxfId="10"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -20856,12 +20858,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T699"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="20" width="25.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="18">
+    <row r="1" spans="1:20" ht="33" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -20923,7 +20925,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:20" ht="18">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>20</v>
       </c>
@@ -20981,7 +20983,7 @@
       </c>
       <c r="T2" s="6"/>
     </row>
-    <row r="3" spans="1:20" ht="18">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
         <v>33</v>
       </c>
@@ -21037,7 +21039,7 @@
       </c>
       <c r="T3" s="6"/>
     </row>
-    <row r="4" spans="1:20" ht="18">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>38</v>
       </c>
@@ -21095,7 +21097,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="5" spans="1:20" ht="18">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
         <v>43</v>
       </c>
@@ -21153,7 +21155,7 @@
       </c>
       <c r="T5" s="6"/>
     </row>
-    <row r="6" spans="1:20" ht="18">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>46</v>
       </c>
@@ -21211,7 +21213,7 @@
       </c>
       <c r="T6" s="6"/>
     </row>
-    <row r="7" spans="1:20" ht="18">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
         <v>48</v>
       </c>
@@ -21269,7 +21271,7 @@
       </c>
       <c r="T7" s="6"/>
     </row>
-    <row r="8" spans="1:20" ht="18">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>49</v>
       </c>
@@ -21327,7 +21329,7 @@
       </c>
       <c r="T8" s="6"/>
     </row>
-    <row r="9" spans="1:20" ht="18">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
         <v>52</v>
       </c>
@@ -21385,7 +21387,7 @@
       </c>
       <c r="T9" s="6"/>
     </row>
-    <row r="10" spans="1:20" ht="18">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>54</v>
       </c>
@@ -21443,7 +21445,7 @@
       </c>
       <c r="T10" s="6"/>
     </row>
-    <row r="11" spans="1:20" ht="18">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
         <v>56</v>
       </c>
@@ -21501,7 +21503,7 @@
       </c>
       <c r="T11" s="6"/>
     </row>
-    <row r="12" spans="1:20" ht="18">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>58</v>
       </c>
@@ -21559,7 +21561,7 @@
       </c>
       <c r="T12" s="6"/>
     </row>
-    <row r="13" spans="1:20" ht="18">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
         <v>60</v>
       </c>
@@ -21617,7 +21619,7 @@
       </c>
       <c r="T13" s="6"/>
     </row>
-    <row r="14" spans="1:20" ht="18">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>62</v>
       </c>
@@ -21675,7 +21677,7 @@
       </c>
       <c r="T14" s="6"/>
     </row>
-    <row r="15" spans="1:20" ht="18">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
         <v>64</v>
       </c>
@@ -21733,7 +21735,7 @@
       </c>
       <c r="T15" s="6"/>
     </row>
-    <row r="16" spans="1:20" ht="18">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>66</v>
       </c>
@@ -21791,7 +21793,7 @@
       </c>
       <c r="T16" s="6"/>
     </row>
-    <row r="17" spans="1:20" ht="18">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
         <v>68</v>
       </c>
@@ -21849,7 +21851,7 @@
       </c>
       <c r="T17" s="6"/>
     </row>
-    <row r="18" spans="1:20" ht="18">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>71</v>
       </c>
@@ -21907,7 +21909,7 @@
       </c>
       <c r="T18" s="6"/>
     </row>
-    <row r="19" spans="1:20" ht="18">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
         <v>78</v>
       </c>
@@ -21965,7 +21967,7 @@
       </c>
       <c r="T19" s="6"/>
     </row>
-    <row r="20" spans="1:20" ht="18">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>80</v>
       </c>
@@ -22023,7 +22025,7 @@
       </c>
       <c r="T20" s="6"/>
     </row>
-    <row r="21" spans="1:20" ht="18">
+    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
         <v>82</v>
       </c>
@@ -22081,7 +22083,7 @@
       </c>
       <c r="T21" s="6"/>
     </row>
-    <row r="22" spans="1:20" ht="18">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>84</v>
       </c>
@@ -22139,7 +22141,7 @@
       </c>
       <c r="T22" s="6"/>
     </row>
-    <row r="23" spans="1:20" ht="18">
+    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
         <v>86</v>
       </c>
@@ -22197,7 +22199,7 @@
       </c>
       <c r="T23" s="6"/>
     </row>
-    <row r="24" spans="1:20" ht="18">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>89</v>
       </c>
@@ -22255,7 +22257,7 @@
       </c>
       <c r="T24" s="6"/>
     </row>
-    <row r="25" spans="1:20" ht="18">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
         <v>91</v>
       </c>
@@ -22311,7 +22313,7 @@
       </c>
       <c r="T25" s="6"/>
     </row>
-    <row r="26" spans="1:20" ht="18">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>95</v>
       </c>
@@ -22369,7 +22371,7 @@
       </c>
       <c r="T26" s="6"/>
     </row>
-    <row r="27" spans="1:20" ht="18">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
         <v>99</v>
       </c>
@@ -22427,7 +22429,7 @@
       </c>
       <c r="T27" s="6"/>
     </row>
-    <row r="28" spans="1:20" ht="18">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>102</v>
       </c>
@@ -22485,7 +22487,7 @@
       </c>
       <c r="T28" s="6"/>
     </row>
-    <row r="29" spans="1:20" ht="18">
+    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
         <v>104</v>
       </c>
@@ -22543,7 +22545,7 @@
       </c>
       <c r="T29" s="6"/>
     </row>
-    <row r="30" spans="1:20" ht="18">
+    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>106</v>
       </c>
@@ -22601,7 +22603,7 @@
       </c>
       <c r="T30" s="6"/>
     </row>
-    <row r="31" spans="1:20" ht="18">
+    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
         <v>108</v>
       </c>
@@ -22659,7 +22661,7 @@
       </c>
       <c r="T31" s="6"/>
     </row>
-    <row r="32" spans="1:20" ht="18">
+    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>109</v>
       </c>
@@ -22717,7 +22719,7 @@
       </c>
       <c r="T32" s="6"/>
     </row>
-    <row r="33" spans="1:20" ht="18">
+    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
         <v>111</v>
       </c>
@@ -22775,7 +22777,7 @@
       </c>
       <c r="T33" s="6"/>
     </row>
-    <row r="34" spans="1:20" ht="18">
+    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>112</v>
       </c>
@@ -22833,7 +22835,7 @@
       </c>
       <c r="T34" s="6"/>
     </row>
-    <row r="35" spans="1:20" ht="18">
+    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
         <v>113</v>
       </c>
@@ -22891,7 +22893,7 @@
       </c>
       <c r="T35" s="6"/>
     </row>
-    <row r="36" spans="1:20" ht="18">
+    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>114</v>
       </c>
@@ -22949,7 +22951,7 @@
       </c>
       <c r="T36" s="6"/>
     </row>
-    <row r="37" spans="1:20" ht="18">
+    <row r="37" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
         <v>115</v>
       </c>
@@ -23007,7 +23009,7 @@
       </c>
       <c r="T37" s="6"/>
     </row>
-    <row r="38" spans="1:20" ht="18">
+    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>117</v>
       </c>
@@ -23065,7 +23067,7 @@
       </c>
       <c r="T38" s="6"/>
     </row>
-    <row r="39" spans="1:20" ht="18">
+    <row r="39" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
         <v>119</v>
       </c>
@@ -23123,7 +23125,7 @@
       </c>
       <c r="T39" s="6"/>
     </row>
-    <row r="40" spans="1:20" ht="18">
+    <row r="40" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
         <v>122</v>
       </c>
@@ -23181,7 +23183,7 @@
       </c>
       <c r="T40" s="6"/>
     </row>
-    <row r="41" spans="1:20" ht="18">
+    <row r="41" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
         <v>126</v>
       </c>
@@ -23239,7 +23241,7 @@
       </c>
       <c r="T41" s="6"/>
     </row>
-    <row r="42" spans="1:20" ht="18">
+    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
         <v>131</v>
       </c>
@@ -23297,7 +23299,7 @@
       </c>
       <c r="T42" s="6"/>
     </row>
-    <row r="43" spans="1:20" ht="18">
+    <row r="43" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
         <v>132</v>
       </c>
@@ -23355,7 +23357,7 @@
       </c>
       <c r="T43" s="6"/>
     </row>
-    <row r="44" spans="1:20" ht="18">
+    <row r="44" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
         <v>135</v>
       </c>
@@ -23413,7 +23415,7 @@
       </c>
       <c r="T44" s="6"/>
     </row>
-    <row r="45" spans="1:20" ht="18">
+    <row r="45" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
         <v>136</v>
       </c>
@@ -23471,7 +23473,7 @@
       </c>
       <c r="T45" s="6"/>
     </row>
-    <row r="46" spans="1:20" ht="18">
+    <row r="46" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
         <v>137</v>
       </c>
@@ -23529,7 +23531,7 @@
       </c>
       <c r="T46" s="6"/>
     </row>
-    <row r="47" spans="1:20" ht="18">
+    <row r="47" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
         <v>139</v>
       </c>
@@ -23587,7 +23589,7 @@
       </c>
       <c r="T47" s="6"/>
     </row>
-    <row r="48" spans="1:20" ht="18">
+    <row r="48" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
         <v>141</v>
       </c>
@@ -23645,7 +23647,7 @@
       </c>
       <c r="T48" s="6"/>
     </row>
-    <row r="49" spans="1:20" ht="18">
+    <row r="49" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
         <v>143</v>
       </c>
@@ -23703,7 +23705,7 @@
       </c>
       <c r="T49" s="6"/>
     </row>
-    <row r="50" spans="1:20" ht="18">
+    <row r="50" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
         <v>144</v>
       </c>
@@ -23761,7 +23763,7 @@
       </c>
       <c r="T50" s="6"/>
     </row>
-    <row r="51" spans="1:20" ht="18">
+    <row r="51" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
         <v>146</v>
       </c>
@@ -23819,7 +23821,7 @@
       </c>
       <c r="T51" s="6"/>
     </row>
-    <row r="52" spans="1:20" ht="18">
+    <row r="52" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
         <v>147</v>
       </c>
@@ -23877,7 +23879,7 @@
       </c>
       <c r="T52" s="6"/>
     </row>
-    <row r="53" spans="1:20" ht="18">
+    <row r="53" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
         <v>149</v>
       </c>
@@ -23935,7 +23937,7 @@
       </c>
       <c r="T53" s="6"/>
     </row>
-    <row r="54" spans="1:20" ht="18">
+    <row r="54" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
         <v>150</v>
       </c>
@@ -23993,7 +23995,7 @@
       </c>
       <c r="T54" s="6"/>
     </row>
-    <row r="55" spans="1:20" ht="18">
+    <row r="55" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
         <v>152</v>
       </c>
@@ -24051,7 +24053,7 @@
       </c>
       <c r="T55" s="6"/>
     </row>
-    <row r="56" spans="1:20" ht="18">
+    <row r="56" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
         <v>153</v>
       </c>
@@ -24109,7 +24111,7 @@
       </c>
       <c r="T56" s="6"/>
     </row>
-    <row r="57" spans="1:20" ht="18">
+    <row r="57" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
         <v>154</v>
       </c>
@@ -24167,7 +24169,7 @@
       </c>
       <c r="T57" s="6"/>
     </row>
-    <row r="58" spans="1:20" ht="18">
+    <row r="58" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
         <v>155</v>
       </c>
@@ -24225,7 +24227,7 @@
       </c>
       <c r="T58" s="6"/>
     </row>
-    <row r="59" spans="1:20" ht="18">
+    <row r="59" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
         <v>157</v>
       </c>
@@ -24283,7 +24285,7 @@
       </c>
       <c r="T59" s="6"/>
     </row>
-    <row r="60" spans="1:20" ht="18">
+    <row r="60" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
         <v>159</v>
       </c>
@@ -24341,7 +24343,7 @@
       </c>
       <c r="T60" s="6"/>
     </row>
-    <row r="61" spans="1:20" ht="18">
+    <row r="61" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
         <v>161</v>
       </c>
@@ -24399,7 +24401,7 @@
       </c>
       <c r="T61" s="6"/>
     </row>
-    <row r="62" spans="1:20" ht="18">
+    <row r="62" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
         <v>164</v>
       </c>
@@ -24457,7 +24459,7 @@
       </c>
       <c r="T62" s="6"/>
     </row>
-    <row r="63" spans="1:20" ht="18">
+    <row r="63" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
         <v>166</v>
       </c>
@@ -24515,7 +24517,7 @@
       </c>
       <c r="T63" s="6"/>
     </row>
-    <row r="64" spans="1:20" ht="18">
+    <row r="64" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
         <v>168</v>
       </c>
@@ -24573,7 +24575,7 @@
       </c>
       <c r="T64" s="6"/>
     </row>
-    <row r="65" spans="1:20" ht="18">
+    <row r="65" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
         <v>169</v>
       </c>
@@ -24631,7 +24633,7 @@
       </c>
       <c r="T65" s="6"/>
     </row>
-    <row r="66" spans="1:20" ht="18">
+    <row r="66" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
         <v>173</v>
       </c>
@@ -24689,7 +24691,7 @@
       </c>
       <c r="T66" s="6"/>
     </row>
-    <row r="67" spans="1:20" ht="18">
+    <row r="67" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
         <v>175</v>
       </c>
@@ -24747,7 +24749,7 @@
       </c>
       <c r="T67" s="6"/>
     </row>
-    <row r="68" spans="1:20" ht="18">
+    <row r="68" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
         <v>177</v>
       </c>
@@ -24805,7 +24807,7 @@
       </c>
       <c r="T68" s="6"/>
     </row>
-    <row r="69" spans="1:20" ht="18">
+    <row r="69" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
         <v>179</v>
       </c>
@@ -24863,7 +24865,7 @@
       </c>
       <c r="T69" s="6"/>
     </row>
-    <row r="70" spans="1:20" ht="18">
+    <row r="70" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
         <v>181</v>
       </c>
@@ -24921,7 +24923,7 @@
       </c>
       <c r="T70" s="6"/>
     </row>
-    <row r="71" spans="1:20" ht="18">
+    <row r="71" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
         <v>183</v>
       </c>
@@ -24979,7 +24981,7 @@
       </c>
       <c r="T71" s="6"/>
     </row>
-    <row r="72" spans="1:20" ht="18">
+    <row r="72" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
         <v>185</v>
       </c>
@@ -25037,7 +25039,7 @@
       </c>
       <c r="T72" s="6"/>
     </row>
-    <row r="73" spans="1:20" ht="18">
+    <row r="73" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
         <v>187</v>
       </c>
@@ -25095,7 +25097,7 @@
       </c>
       <c r="T73" s="6"/>
     </row>
-    <row r="74" spans="1:20" ht="18">
+    <row r="74" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
         <v>189</v>
       </c>
@@ -25153,7 +25155,7 @@
       </c>
       <c r="T74" s="6"/>
     </row>
-    <row r="75" spans="1:20" ht="18">
+    <row r="75" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
         <v>190</v>
       </c>
@@ -25211,7 +25213,7 @@
       </c>
       <c r="T75" s="6"/>
     </row>
-    <row r="76" spans="1:20" ht="18">
+    <row r="76" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
         <v>192</v>
       </c>
@@ -25269,7 +25271,7 @@
       </c>
       <c r="T76" s="6"/>
     </row>
-    <row r="77" spans="1:20" ht="18">
+    <row r="77" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
         <v>193</v>
       </c>
@@ -25327,7 +25329,7 @@
       </c>
       <c r="T77" s="6"/>
     </row>
-    <row r="78" spans="1:20" ht="18">
+    <row r="78" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
         <v>195</v>
       </c>
@@ -25385,7 +25387,7 @@
       </c>
       <c r="T78" s="6"/>
     </row>
-    <row r="79" spans="1:20" ht="18">
+    <row r="79" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
         <v>196</v>
       </c>
@@ -25443,7 +25445,7 @@
       </c>
       <c r="T79" s="6"/>
     </row>
-    <row r="80" spans="1:20" ht="18">
+    <row r="80" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
         <v>198</v>
       </c>
@@ -25501,7 +25503,7 @@
       </c>
       <c r="T80" s="6"/>
     </row>
-    <row r="81" spans="1:20" ht="18">
+    <row r="81" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
         <v>200</v>
       </c>
@@ -25559,7 +25561,7 @@
       </c>
       <c r="T81" s="6"/>
     </row>
-    <row r="82" spans="1:20" ht="18">
+    <row r="82" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
         <v>202</v>
       </c>
@@ -25617,7 +25619,7 @@
       </c>
       <c r="T82" s="6"/>
     </row>
-    <row r="83" spans="1:20" ht="18">
+    <row r="83" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
         <v>204</v>
       </c>
@@ -25675,7 +25677,7 @@
       </c>
       <c r="T83" s="6"/>
     </row>
-    <row r="84" spans="1:20" ht="18">
+    <row r="84" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
         <v>205</v>
       </c>
@@ -25733,7 +25735,7 @@
       </c>
       <c r="T84" s="6"/>
     </row>
-    <row r="85" spans="1:20" ht="18">
+    <row r="85" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
         <v>208</v>
       </c>
@@ -25791,7 +25793,7 @@
       </c>
       <c r="T85" s="6"/>
     </row>
-    <row r="86" spans="1:20" ht="18">
+    <row r="86" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
         <v>209</v>
       </c>
@@ -25849,7 +25851,7 @@
       </c>
       <c r="T86" s="6"/>
     </row>
-    <row r="87" spans="1:20" ht="18">
+    <row r="87" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
         <v>210</v>
       </c>
@@ -25907,7 +25909,7 @@
       </c>
       <c r="T87" s="6"/>
     </row>
-    <row r="88" spans="1:20" ht="18">
+    <row r="88" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
         <v>212</v>
       </c>
@@ -25965,7 +25967,7 @@
       </c>
       <c r="T88" s="6"/>
     </row>
-    <row r="89" spans="1:20" ht="18">
+    <row r="89" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
         <v>214</v>
       </c>
@@ -26023,7 +26025,7 @@
       </c>
       <c r="T89" s="6"/>
     </row>
-    <row r="90" spans="1:20" ht="18">
+    <row r="90" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
         <v>216</v>
       </c>
@@ -26081,7 +26083,7 @@
       </c>
       <c r="T90" s="6"/>
     </row>
-    <row r="91" spans="1:20" ht="18">
+    <row r="91" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
         <v>217</v>
       </c>
@@ -26139,7 +26141,7 @@
       </c>
       <c r="T91" s="6"/>
     </row>
-    <row r="92" spans="1:20" ht="18">
+    <row r="92" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
         <v>218</v>
       </c>
@@ -26197,7 +26199,7 @@
       </c>
       <c r="T92" s="6"/>
     </row>
-    <row r="93" spans="1:20" ht="18">
+    <row r="93" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
         <v>222</v>
       </c>
@@ -26255,7 +26257,7 @@
       </c>
       <c r="T93" s="6"/>
     </row>
-    <row r="94" spans="1:20" ht="18">
+    <row r="94" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
         <v>224</v>
       </c>
@@ -26313,7 +26315,7 @@
       </c>
       <c r="T94" s="6"/>
     </row>
-    <row r="95" spans="1:20" ht="18">
+    <row r="95" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
         <v>226</v>
       </c>
@@ -26371,7 +26373,7 @@
       </c>
       <c r="T95" s="6"/>
     </row>
-    <row r="96" spans="1:20" ht="18">
+    <row r="96" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
         <v>227</v>
       </c>
@@ -26429,7 +26431,7 @@
       </c>
       <c r="T96" s="6"/>
     </row>
-    <row r="97" spans="1:20" ht="18">
+    <row r="97" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
         <v>231</v>
       </c>
@@ -26487,7 +26489,7 @@
       </c>
       <c r="T97" s="6"/>
     </row>
-    <row r="98" spans="1:20" ht="18">
+    <row r="98" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
         <v>233</v>
       </c>
@@ -26545,7 +26547,7 @@
       </c>
       <c r="T98" s="6"/>
     </row>
-    <row r="99" spans="1:20" ht="18">
+    <row r="99" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
         <v>234</v>
       </c>
@@ -26603,7 +26605,7 @@
       </c>
       <c r="T99" s="6"/>
     </row>
-    <row r="100" spans="1:20" ht="18">
+    <row r="100" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A100" s="3" t="s">
         <v>236</v>
       </c>
@@ -26661,7 +26663,7 @@
       </c>
       <c r="T100" s="6"/>
     </row>
-    <row r="101" spans="1:20" ht="18">
+    <row r="101" spans="1:20" ht="99.75" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
         <v>238</v>
       </c>
@@ -26721,7 +26723,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="102" spans="1:20" ht="18">
+    <row r="102" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A102" s="3" t="s">
         <v>242</v>
       </c>
@@ -26779,7 +26781,7 @@
       </c>
       <c r="T102" s="6"/>
     </row>
-    <row r="103" spans="1:20" ht="18">
+    <row r="103" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
         <v>244</v>
       </c>
@@ -26837,7 +26839,7 @@
       </c>
       <c r="T103" s="6"/>
     </row>
-    <row r="104" spans="1:20" ht="18">
+    <row r="104" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A104" s="3" t="s">
         <v>245</v>
       </c>
@@ -26895,7 +26897,7 @@
       </c>
       <c r="T104" s="6"/>
     </row>
-    <row r="105" spans="1:20" ht="18">
+    <row r="105" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
         <v>246</v>
       </c>
@@ -26953,7 +26955,7 @@
       </c>
       <c r="T105" s="6"/>
     </row>
-    <row r="106" spans="1:20" ht="18">
+    <row r="106" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A106" s="3" t="s">
         <v>247</v>
       </c>
@@ -27011,7 +27013,7 @@
       </c>
       <c r="T106" s="6"/>
     </row>
-    <row r="107" spans="1:20" ht="18">
+    <row r="107" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
         <v>251</v>
       </c>
@@ -27069,7 +27071,7 @@
       </c>
       <c r="T107" s="6"/>
     </row>
-    <row r="108" spans="1:20" ht="18">
+    <row r="108" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A108" s="3" t="s">
         <v>252</v>
       </c>
@@ -27127,7 +27129,7 @@
       </c>
       <c r="T108" s="6"/>
     </row>
-    <row r="109" spans="1:20" ht="18">
+    <row r="109" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
         <v>254</v>
       </c>
@@ -27185,7 +27187,7 @@
       </c>
       <c r="T109" s="6"/>
     </row>
-    <row r="110" spans="1:20" ht="18">
+    <row r="110" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A110" s="3" t="s">
         <v>259</v>
       </c>
@@ -27243,7 +27245,7 @@
       </c>
       <c r="T110" s="6"/>
     </row>
-    <row r="111" spans="1:20" ht="18">
+    <row r="111" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A111" s="7" t="s">
         <v>261</v>
       </c>
@@ -27301,7 +27303,7 @@
       </c>
       <c r="T111" s="6"/>
     </row>
-    <row r="112" spans="1:20" ht="18">
+    <row r="112" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A112" s="3" t="s">
         <v>263</v>
       </c>
@@ -27359,7 +27361,7 @@
       </c>
       <c r="T112" s="6"/>
     </row>
-    <row r="113" spans="1:20" ht="18">
+    <row r="113" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A113" s="7" t="s">
         <v>264</v>
       </c>
@@ -27417,7 +27419,7 @@
       </c>
       <c r="T113" s="6"/>
     </row>
-    <row r="114" spans="1:20" ht="18">
+    <row r="114" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A114" s="3" t="s">
         <v>266</v>
       </c>
@@ -27475,7 +27477,7 @@
       </c>
       <c r="T114" s="6"/>
     </row>
-    <row r="115" spans="1:20" ht="18">
+    <row r="115" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A115" s="7" t="s">
         <v>268</v>
       </c>
@@ -27533,7 +27535,7 @@
       </c>
       <c r="T115" s="6"/>
     </row>
-    <row r="116" spans="1:20" ht="18">
+    <row r="116" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A116" s="3" t="s">
         <v>269</v>
       </c>
@@ -27591,7 +27593,7 @@
       </c>
       <c r="T116" s="6"/>
     </row>
-    <row r="117" spans="1:20" ht="18">
+    <row r="117" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A117" s="7" t="s">
         <v>271</v>
       </c>
@@ -27649,7 +27651,7 @@
       </c>
       <c r="T117" s="6"/>
     </row>
-    <row r="118" spans="1:20" ht="18">
+    <row r="118" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A118" s="3" t="s">
         <v>272</v>
       </c>
@@ -27707,7 +27709,7 @@
       </c>
       <c r="T118" s="6"/>
     </row>
-    <row r="119" spans="1:20" ht="18">
+    <row r="119" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A119" s="7" t="s">
         <v>274</v>
       </c>
@@ -27765,7 +27767,7 @@
       </c>
       <c r="T119" s="6"/>
     </row>
-    <row r="120" spans="1:20" ht="18">
+    <row r="120" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A120" s="3" t="s">
         <v>275</v>
       </c>
@@ -27823,7 +27825,7 @@
       </c>
       <c r="T120" s="6"/>
     </row>
-    <row r="121" spans="1:20" ht="18">
+    <row r="121" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A121" s="7" t="s">
         <v>276</v>
       </c>
@@ -27881,7 +27883,7 @@
       </c>
       <c r="T121" s="6"/>
     </row>
-    <row r="122" spans="1:20" ht="18">
+    <row r="122" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A122" s="3" t="s">
         <v>277</v>
       </c>
@@ -27939,7 +27941,7 @@
       </c>
       <c r="T122" s="6"/>
     </row>
-    <row r="123" spans="1:20" ht="18">
+    <row r="123" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A123" s="7" t="s">
         <v>278</v>
       </c>
@@ -27997,7 +27999,7 @@
       </c>
       <c r="T123" s="6"/>
     </row>
-    <row r="124" spans="1:20" ht="18">
+    <row r="124" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A124" s="3" t="s">
         <v>282</v>
       </c>
@@ -28055,7 +28057,7 @@
       </c>
       <c r="T124" s="6"/>
     </row>
-    <row r="125" spans="1:20" ht="18">
+    <row r="125" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A125" s="7" t="s">
         <v>284</v>
       </c>
@@ -28113,7 +28115,7 @@
       </c>
       <c r="T125" s="6"/>
     </row>
-    <row r="126" spans="1:20" ht="18">
+    <row r="126" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A126" s="3" t="s">
         <v>287</v>
       </c>
@@ -28171,7 +28173,7 @@
       </c>
       <c r="T126" s="6"/>
     </row>
-    <row r="127" spans="1:20" ht="18">
+    <row r="127" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A127" s="7" t="s">
         <v>288</v>
       </c>
@@ -28229,7 +28231,7 @@
       </c>
       <c r="T127" s="6"/>
     </row>
-    <row r="128" spans="1:20" ht="18">
+    <row r="128" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A128" s="3" t="s">
         <v>289</v>
       </c>
@@ -28287,7 +28289,7 @@
       </c>
       <c r="T128" s="6"/>
     </row>
-    <row r="129" spans="1:20" ht="18">
+    <row r="129" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A129" s="7" t="s">
         <v>290</v>
       </c>
@@ -28345,7 +28347,7 @@
       </c>
       <c r="T129" s="6"/>
     </row>
-    <row r="130" spans="1:20" ht="18">
+    <row r="130" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A130" s="3" t="s">
         <v>295</v>
       </c>
@@ -28403,7 +28405,7 @@
       </c>
       <c r="T130" s="6"/>
     </row>
-    <row r="131" spans="1:20" ht="18">
+    <row r="131" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A131" s="7" t="s">
         <v>296</v>
       </c>
@@ -28461,7 +28463,7 @@
       </c>
       <c r="T131" s="6"/>
     </row>
-    <row r="132" spans="1:20" ht="18">
+    <row r="132" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A132" s="3" t="s">
         <v>297</v>
       </c>
@@ -28519,7 +28521,7 @@
       </c>
       <c r="T132" s="6"/>
     </row>
-    <row r="133" spans="1:20" ht="18">
+    <row r="133" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A133" s="7" t="s">
         <v>299</v>
       </c>
@@ -28577,7 +28579,7 @@
       </c>
       <c r="T133" s="6"/>
     </row>
-    <row r="134" spans="1:20" ht="18">
+    <row r="134" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A134" s="3" t="s">
         <v>300</v>
       </c>
@@ -28635,7 +28637,7 @@
       </c>
       <c r="T134" s="6"/>
     </row>
-    <row r="135" spans="1:20" ht="18">
+    <row r="135" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A135" s="7" t="s">
         <v>302</v>
       </c>
@@ -28693,7 +28695,7 @@
       </c>
       <c r="T135" s="6"/>
     </row>
-    <row r="136" spans="1:20" ht="18">
+    <row r="136" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A136" s="3" t="s">
         <v>303</v>
       </c>
@@ -28751,7 +28753,7 @@
       </c>
       <c r="T136" s="6"/>
     </row>
-    <row r="137" spans="1:20" ht="18">
+    <row r="137" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A137" s="7" t="s">
         <v>305</v>
       </c>
@@ -28809,7 +28811,7 @@
       </c>
       <c r="T137" s="6"/>
     </row>
-    <row r="138" spans="1:20" ht="18">
+    <row r="138" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A138" s="3" t="s">
         <v>310</v>
       </c>
@@ -28867,7 +28869,7 @@
       </c>
       <c r="T138" s="6"/>
     </row>
-    <row r="139" spans="1:20" ht="18">
+    <row r="139" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A139" s="7" t="s">
         <v>315</v>
       </c>
@@ -28925,7 +28927,7 @@
       </c>
       <c r="T139" s="6"/>
     </row>
-    <row r="140" spans="1:20" ht="18">
+    <row r="140" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A140" s="3" t="s">
         <v>316</v>
       </c>
@@ -28983,7 +28985,7 @@
       </c>
       <c r="T140" s="6"/>
     </row>
-    <row r="141" spans="1:20" ht="18">
+    <row r="141" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A141" s="7" t="s">
         <v>317</v>
       </c>
@@ -29037,7 +29039,7 @@
       </c>
       <c r="T141" s="6"/>
     </row>
-    <row r="142" spans="1:20" ht="18">
+    <row r="142" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A142" s="3" t="s">
         <v>322</v>
       </c>
@@ -29095,7 +29097,7 @@
       </c>
       <c r="T142" s="6"/>
     </row>
-    <row r="143" spans="1:20" ht="18">
+    <row r="143" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A143" s="7" t="s">
         <v>323</v>
       </c>
@@ -29153,7 +29155,7 @@
       </c>
       <c r="T143" s="6"/>
     </row>
-    <row r="144" spans="1:20" ht="18">
+    <row r="144" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A144" s="3" t="s">
         <v>324</v>
       </c>
@@ -29211,7 +29213,7 @@
       </c>
       <c r="T144" s="6"/>
     </row>
-    <row r="145" spans="1:20" ht="18">
+    <row r="145" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A145" s="7" t="s">
         <v>328</v>
       </c>
@@ -29269,7 +29271,7 @@
       </c>
       <c r="T145" s="6"/>
     </row>
-    <row r="146" spans="1:20" ht="18">
+    <row r="146" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A146" s="3" t="s">
         <v>330</v>
       </c>
@@ -29327,7 +29329,7 @@
       </c>
       <c r="T146" s="6"/>
     </row>
-    <row r="147" spans="1:20" ht="18">
+    <row r="147" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A147" s="7" t="s">
         <v>332</v>
       </c>
@@ -29385,7 +29387,7 @@
       </c>
       <c r="T147" s="6"/>
     </row>
-    <row r="148" spans="1:20" ht="18">
+    <row r="148" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A148" s="3" t="s">
         <v>334</v>
       </c>
@@ -29443,7 +29445,7 @@
       </c>
       <c r="T148" s="6"/>
     </row>
-    <row r="149" spans="1:20" ht="18">
+    <row r="149" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A149" s="7" t="s">
         <v>335</v>
       </c>
@@ -29501,7 +29503,7 @@
       </c>
       <c r="T149" s="6"/>
     </row>
-    <row r="150" spans="1:20" ht="18">
+    <row r="150" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A150" s="3" t="s">
         <v>337</v>
       </c>
@@ -29559,7 +29561,7 @@
       </c>
       <c r="T150" s="6"/>
     </row>
-    <row r="151" spans="1:20" ht="18">
+    <row r="151" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A151" s="7" t="s">
         <v>339</v>
       </c>
@@ -29617,7 +29619,7 @@
       </c>
       <c r="T151" s="6"/>
     </row>
-    <row r="152" spans="1:20" ht="18">
+    <row r="152" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A152" s="3" t="s">
         <v>340</v>
       </c>
@@ -29675,7 +29677,7 @@
       </c>
       <c r="T152" s="6"/>
     </row>
-    <row r="153" spans="1:20" ht="18">
+    <row r="153" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A153" s="7" t="s">
         <v>341</v>
       </c>
@@ -29733,7 +29735,7 @@
       </c>
       <c r="T153" s="6"/>
     </row>
-    <row r="154" spans="1:20" ht="18">
+    <row r="154" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A154" s="3" t="s">
         <v>342</v>
       </c>
@@ -29791,7 +29793,7 @@
       </c>
       <c r="T154" s="6"/>
     </row>
-    <row r="155" spans="1:20" ht="18">
+    <row r="155" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A155" s="7" t="s">
         <v>343</v>
       </c>
@@ -29849,7 +29851,7 @@
       </c>
       <c r="T155" s="6"/>
     </row>
-    <row r="156" spans="1:20" ht="18">
+    <row r="156" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A156" s="3" t="s">
         <v>344</v>
       </c>
@@ -29907,7 +29909,7 @@
       </c>
       <c r="T156" s="6"/>
     </row>
-    <row r="157" spans="1:20" ht="18">
+    <row r="157" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A157" s="7" t="s">
         <v>347</v>
       </c>
@@ -29965,7 +29967,7 @@
       </c>
       <c r="T157" s="6"/>
     </row>
-    <row r="158" spans="1:20" ht="18">
+    <row r="158" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A158" s="3" t="s">
         <v>349</v>
       </c>
@@ -30023,7 +30025,7 @@
       </c>
       <c r="T158" s="6"/>
     </row>
-    <row r="159" spans="1:20" ht="18">
+    <row r="159" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A159" s="7" t="s">
         <v>351</v>
       </c>
@@ -30081,7 +30083,7 @@
       </c>
       <c r="T159" s="6"/>
     </row>
-    <row r="160" spans="1:20" ht="18">
+    <row r="160" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A160" s="3" t="s">
         <v>352</v>
       </c>
@@ -30139,7 +30141,7 @@
       </c>
       <c r="T160" s="6"/>
     </row>
-    <row r="161" spans="1:20" ht="18">
+    <row r="161" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A161" s="7" t="s">
         <v>354</v>
       </c>
@@ -30197,7 +30199,7 @@
       </c>
       <c r="T161" s="6"/>
     </row>
-    <row r="162" spans="1:20" ht="18">
+    <row r="162" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A162" s="3" t="s">
         <v>356</v>
       </c>
@@ -30255,7 +30257,7 @@
       </c>
       <c r="T162" s="6"/>
     </row>
-    <row r="163" spans="1:20" ht="18">
+    <row r="163" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A163" s="7" t="s">
         <v>358</v>
       </c>
@@ -30313,7 +30315,7 @@
       </c>
       <c r="T163" s="6"/>
     </row>
-    <row r="164" spans="1:20" ht="18">
+    <row r="164" spans="1:20" ht="42.75" x14ac:dyDescent="0.25">
       <c r="A164" s="3" t="s">
         <v>359</v>
       </c>
@@ -30373,7 +30375,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="165" spans="1:20" ht="18">
+    <row r="165" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A165" s="7" t="s">
         <v>364</v>
       </c>
@@ -30431,7 +30433,7 @@
       </c>
       <c r="T165" s="6"/>
     </row>
-    <row r="166" spans="1:20" ht="18">
+    <row r="166" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A166" s="3" t="s">
         <v>369</v>
       </c>
@@ -30489,7 +30491,7 @@
       </c>
       <c r="T166" s="6"/>
     </row>
-    <row r="167" spans="1:20" ht="18">
+    <row r="167" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A167" s="7" t="s">
         <v>374</v>
       </c>
@@ -30547,7 +30549,7 @@
       </c>
       <c r="T167" s="6"/>
     </row>
-    <row r="168" spans="1:20" ht="18">
+    <row r="168" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A168" s="3" t="s">
         <v>376</v>
       </c>
@@ -30605,7 +30607,7 @@
       </c>
       <c r="T168" s="6"/>
     </row>
-    <row r="169" spans="1:20" ht="18">
+    <row r="169" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A169" s="7" t="s">
         <v>378</v>
       </c>
@@ -30663,7 +30665,7 @@
       </c>
       <c r="T169" s="6"/>
     </row>
-    <row r="170" spans="1:20" ht="18">
+    <row r="170" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A170" s="3" t="s">
         <v>382</v>
       </c>
@@ -30721,7 +30723,7 @@
       </c>
       <c r="T170" s="6"/>
     </row>
-    <row r="171" spans="1:20" ht="18">
+    <row r="171" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A171" s="7" t="s">
         <v>384</v>
       </c>
@@ -30779,7 +30781,7 @@
       </c>
       <c r="T171" s="6"/>
     </row>
-    <row r="172" spans="1:20" ht="18">
+    <row r="172" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A172" s="3" t="s">
         <v>386</v>
       </c>
@@ -30837,7 +30839,7 @@
       </c>
       <c r="T172" s="6"/>
     </row>
-    <row r="173" spans="1:20" ht="18">
+    <row r="173" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A173" s="7" t="s">
         <v>388</v>
       </c>
@@ -30895,7 +30897,7 @@
       </c>
       <c r="T173" s="6"/>
     </row>
-    <row r="174" spans="1:20" ht="18">
+    <row r="174" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A174" s="3" t="s">
         <v>390</v>
       </c>
@@ -30953,7 +30955,7 @@
       </c>
       <c r="T174" s="6"/>
     </row>
-    <row r="175" spans="1:20" ht="18">
+    <row r="175" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A175" s="7" t="s">
         <v>394</v>
       </c>
@@ -31011,7 +31013,7 @@
       </c>
       <c r="T175" s="6"/>
     </row>
-    <row r="176" spans="1:20" ht="18">
+    <row r="176" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A176" s="3" t="s">
         <v>395</v>
       </c>
@@ -31069,7 +31071,7 @@
       </c>
       <c r="T176" s="6"/>
     </row>
-    <row r="177" spans="1:20" ht="18">
+    <row r="177" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A177" s="7" t="s">
         <v>399</v>
       </c>
@@ -31127,7 +31129,7 @@
       </c>
       <c r="T177" s="6"/>
     </row>
-    <row r="178" spans="1:20" ht="18">
+    <row r="178" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A178" s="3" t="s">
         <v>400</v>
       </c>
@@ -31185,7 +31187,7 @@
       </c>
       <c r="T178" s="6"/>
     </row>
-    <row r="179" spans="1:20" ht="18">
+    <row r="179" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A179" s="7" t="s">
         <v>403</v>
       </c>
@@ -31243,7 +31245,7 @@
       </c>
       <c r="T179" s="6"/>
     </row>
-    <row r="180" spans="1:20" ht="18">
+    <row r="180" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A180" s="3" t="s">
         <v>404</v>
       </c>
@@ -31301,7 +31303,7 @@
       </c>
       <c r="T180" s="6"/>
     </row>
-    <row r="181" spans="1:20" ht="18">
+    <row r="181" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A181" s="7" t="s">
         <v>405</v>
       </c>
@@ -31359,7 +31361,7 @@
       </c>
       <c r="T181" s="6"/>
     </row>
-    <row r="182" spans="1:20" ht="18">
+    <row r="182" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A182" s="3" t="s">
         <v>406</v>
       </c>
@@ -31417,7 +31419,7 @@
       </c>
       <c r="T182" s="6"/>
     </row>
-    <row r="183" spans="1:20" ht="18">
+    <row r="183" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A183" s="7" t="s">
         <v>408</v>
       </c>
@@ -31475,7 +31477,7 @@
       </c>
       <c r="T183" s="6"/>
     </row>
-    <row r="184" spans="1:20" ht="18">
+    <row r="184" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A184" s="3" t="s">
         <v>409</v>
       </c>
@@ -31533,7 +31535,7 @@
       </c>
       <c r="T184" s="6"/>
     </row>
-    <row r="185" spans="1:20" ht="18">
+    <row r="185" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A185" s="7" t="s">
         <v>411</v>
       </c>
@@ -31591,7 +31593,7 @@
       </c>
       <c r="T185" s="6"/>
     </row>
-    <row r="186" spans="1:20" ht="18">
+    <row r="186" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A186" s="3" t="s">
         <v>416</v>
       </c>
@@ -31649,7 +31651,7 @@
       </c>
       <c r="T186" s="6"/>
     </row>
-    <row r="187" spans="1:20" ht="18">
+    <row r="187" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A187" s="7" t="s">
         <v>417</v>
       </c>
@@ -31707,7 +31709,7 @@
       </c>
       <c r="T187" s="6"/>
     </row>
-    <row r="188" spans="1:20" ht="18">
+    <row r="188" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A188" s="3" t="s">
         <v>419</v>
       </c>
@@ -31765,7 +31767,7 @@
       </c>
       <c r="T188" s="6"/>
     </row>
-    <row r="189" spans="1:20" ht="18">
+    <row r="189" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A189" s="7" t="s">
         <v>422</v>
       </c>
@@ -31821,7 +31823,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="190" spans="1:20" ht="18">
+    <row r="190" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A190" s="3" t="s">
         <v>425</v>
       </c>
@@ -31879,7 +31881,7 @@
       </c>
       <c r="T190" s="6"/>
     </row>
-    <row r="191" spans="1:20" ht="18">
+    <row r="191" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A191" s="7" t="s">
         <v>426</v>
       </c>
@@ -31937,7 +31939,7 @@
       </c>
       <c r="T191" s="6"/>
     </row>
-    <row r="192" spans="1:20" ht="18">
+    <row r="192" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A192" s="3" t="s">
         <v>427</v>
       </c>
@@ -31995,7 +31997,7 @@
       </c>
       <c r="T192" s="6"/>
     </row>
-    <row r="193" spans="1:20" ht="18">
+    <row r="193" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A193" s="7" t="s">
         <v>428</v>
       </c>
@@ -32053,7 +32055,7 @@
       </c>
       <c r="T193" s="6"/>
     </row>
-    <row r="194" spans="1:20" ht="18">
+    <row r="194" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A194" s="3" t="s">
         <v>429</v>
       </c>
@@ -32111,7 +32113,7 @@
       </c>
       <c r="T194" s="6"/>
     </row>
-    <row r="195" spans="1:20" ht="18">
+    <row r="195" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A195" s="7" t="s">
         <v>430</v>
       </c>
@@ -32169,7 +32171,7 @@
       </c>
       <c r="T195" s="6"/>
     </row>
-    <row r="196" spans="1:20" ht="18">
+    <row r="196" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A196" s="3" t="s">
         <v>431</v>
       </c>
@@ -32227,7 +32229,7 @@
       </c>
       <c r="T196" s="6"/>
     </row>
-    <row r="197" spans="1:20" ht="18">
+    <row r="197" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A197" s="7" t="s">
         <v>432</v>
       </c>
@@ -32285,7 +32287,7 @@
       </c>
       <c r="T197" s="6"/>
     </row>
-    <row r="198" spans="1:20" ht="18">
+    <row r="198" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A198" s="3" t="s">
         <v>433</v>
       </c>
@@ -32343,7 +32345,7 @@
       </c>
       <c r="T198" s="6"/>
     </row>
-    <row r="199" spans="1:20" ht="18">
+    <row r="199" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A199" s="7" t="s">
         <v>437</v>
       </c>
@@ -32401,7 +32403,7 @@
       </c>
       <c r="T199" s="6"/>
     </row>
-    <row r="200" spans="1:20" ht="18">
+    <row r="200" spans="1:20" ht="42.75" x14ac:dyDescent="0.25">
       <c r="A200" s="3" t="s">
         <v>438</v>
       </c>
@@ -32461,7 +32463,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="201" spans="1:20" ht="18">
+    <row r="201" spans="1:20" ht="42.75" x14ac:dyDescent="0.25">
       <c r="A201" s="7" t="s">
         <v>441</v>
       </c>
@@ -32521,7 +32523,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="202" spans="1:20" ht="18">
+    <row r="202" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A202" s="3" t="s">
         <v>442</v>
       </c>
@@ -32579,7 +32581,7 @@
       </c>
       <c r="T202" s="6"/>
     </row>
-    <row r="203" spans="1:20" ht="18">
+    <row r="203" spans="1:20" ht="42.75" x14ac:dyDescent="0.25">
       <c r="A203" s="7" t="s">
         <v>443</v>
       </c>
@@ -32639,7 +32641,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="204" spans="1:20" ht="18">
+    <row r="204" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A204" s="3" t="s">
         <v>448</v>
       </c>
@@ -32697,7 +32699,7 @@
       </c>
       <c r="T204" s="6"/>
     </row>
-    <row r="205" spans="1:20" ht="18">
+    <row r="205" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A205" s="7" t="s">
         <v>449</v>
       </c>
@@ -32755,7 +32757,7 @@
       </c>
       <c r="T205" s="6"/>
     </row>
-    <row r="206" spans="1:20" ht="18">
+    <row r="206" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A206" s="3" t="s">
         <v>450</v>
       </c>
@@ -32813,7 +32815,7 @@
       </c>
       <c r="T206" s="6"/>
     </row>
-    <row r="207" spans="1:20" ht="18">
+    <row r="207" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A207" s="7" t="s">
         <v>452</v>
       </c>
@@ -32871,7 +32873,7 @@
       </c>
       <c r="T207" s="6"/>
     </row>
-    <row r="208" spans="1:20" ht="18">
+    <row r="208" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A208" s="3" t="s">
         <v>454</v>
       </c>
@@ -32929,7 +32931,7 @@
       </c>
       <c r="T208" s="6"/>
     </row>
-    <row r="209" spans="1:20" ht="18">
+    <row r="209" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A209" s="7" t="s">
         <v>455</v>
       </c>
@@ -32987,7 +32989,7 @@
       </c>
       <c r="T209" s="6"/>
     </row>
-    <row r="210" spans="1:20" ht="18">
+    <row r="210" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A210" s="3" t="s">
         <v>458</v>
       </c>
@@ -33045,7 +33047,7 @@
       </c>
       <c r="T210" s="6"/>
     </row>
-    <row r="211" spans="1:20" ht="18">
+    <row r="211" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A211" s="7" t="s">
         <v>459</v>
       </c>
@@ -33103,7 +33105,7 @@
       </c>
       <c r="T211" s="6"/>
     </row>
-    <row r="212" spans="1:20" ht="18">
+    <row r="212" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A212" s="3" t="s">
         <v>460</v>
       </c>
@@ -33161,7 +33163,7 @@
       </c>
       <c r="T212" s="6"/>
     </row>
-    <row r="213" spans="1:20" ht="18">
+    <row r="213" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A213" s="7" t="s">
         <v>463</v>
       </c>
@@ -33215,7 +33217,7 @@
       </c>
       <c r="T213" s="6"/>
     </row>
-    <row r="214" spans="1:20" ht="18">
+    <row r="214" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A214" s="3" t="s">
         <v>464</v>
       </c>
@@ -33275,7 +33277,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="215" spans="1:20" ht="18">
+    <row r="215" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A215" s="7" t="s">
         <v>465</v>
       </c>
@@ -33333,7 +33335,7 @@
       </c>
       <c r="T215" s="6"/>
     </row>
-    <row r="216" spans="1:20" ht="18">
+    <row r="216" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A216" s="3" t="s">
         <v>466</v>
       </c>
@@ -33391,7 +33393,7 @@
       </c>
       <c r="T216" s="6"/>
     </row>
-    <row r="217" spans="1:20" ht="18">
+    <row r="217" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A217" s="7" t="s">
         <v>468</v>
       </c>
@@ -33449,7 +33451,7 @@
       </c>
       <c r="T217" s="6"/>
     </row>
-    <row r="218" spans="1:20" ht="18">
+    <row r="218" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A218" s="3" t="s">
         <v>470</v>
       </c>
@@ -33507,7 +33509,7 @@
       </c>
       <c r="T218" s="6"/>
     </row>
-    <row r="219" spans="1:20" ht="18">
+    <row r="219" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A219" s="7" t="s">
         <v>471</v>
       </c>
@@ -33565,7 +33567,7 @@
       </c>
       <c r="T219" s="6"/>
     </row>
-    <row r="220" spans="1:20" ht="18">
+    <row r="220" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A220" s="3" t="s">
         <v>472</v>
       </c>
@@ -33623,7 +33625,7 @@
       </c>
       <c r="T220" s="6"/>
     </row>
-    <row r="221" spans="1:20" ht="18">
+    <row r="221" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A221" s="7" t="s">
         <v>473</v>
       </c>
@@ -33681,7 +33683,7 @@
       </c>
       <c r="T221" s="6"/>
     </row>
-    <row r="222" spans="1:20" ht="18">
+    <row r="222" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A222" s="3" t="s">
         <v>475</v>
       </c>
@@ -33739,7 +33741,7 @@
       </c>
       <c r="T222" s="6"/>
     </row>
-    <row r="223" spans="1:20" ht="18">
+    <row r="223" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A223" s="7" t="s">
         <v>476</v>
       </c>
@@ -33797,7 +33799,7 @@
       </c>
       <c r="T223" s="6"/>
     </row>
-    <row r="224" spans="1:20" ht="18">
+    <row r="224" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A224" s="3" t="s">
         <v>477</v>
       </c>
@@ -33855,7 +33857,7 @@
       </c>
       <c r="T224" s="6"/>
     </row>
-    <row r="225" spans="1:20" ht="18">
+    <row r="225" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A225" s="7" t="s">
         <v>478</v>
       </c>
@@ -33913,7 +33915,7 @@
       </c>
       <c r="T225" s="6"/>
     </row>
-    <row r="226" spans="1:20" ht="18">
+    <row r="226" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A226" s="3" t="s">
         <v>479</v>
       </c>
@@ -33971,7 +33973,7 @@
       </c>
       <c r="T226" s="6"/>
     </row>
-    <row r="227" spans="1:20" ht="18">
+    <row r="227" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A227" s="7" t="s">
         <v>481</v>
       </c>
@@ -34029,7 +34031,7 @@
       </c>
       <c r="T227" s="6"/>
     </row>
-    <row r="228" spans="1:20" ht="18">
+    <row r="228" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A228" s="3" t="s">
         <v>483</v>
       </c>
@@ -34087,7 +34089,7 @@
       </c>
       <c r="T228" s="6"/>
     </row>
-    <row r="229" spans="1:20" ht="18">
+    <row r="229" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A229" s="7" t="s">
         <v>487</v>
       </c>
@@ -34145,7 +34147,7 @@
       </c>
       <c r="T229" s="6"/>
     </row>
-    <row r="230" spans="1:20" ht="18">
+    <row r="230" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A230" s="3" t="s">
         <v>488</v>
       </c>
@@ -34203,7 +34205,7 @@
       </c>
       <c r="T230" s="6"/>
     </row>
-    <row r="231" spans="1:20" ht="18">
+    <row r="231" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A231" s="7" t="s">
         <v>489</v>
       </c>
@@ -34261,7 +34263,7 @@
       </c>
       <c r="T231" s="6"/>
     </row>
-    <row r="232" spans="1:20" ht="18">
+    <row r="232" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A232" s="3" t="s">
         <v>491</v>
       </c>
@@ -34319,7 +34321,7 @@
       </c>
       <c r="T232" s="6"/>
     </row>
-    <row r="233" spans="1:20" ht="18">
+    <row r="233" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A233" s="7" t="s">
         <v>492</v>
       </c>
@@ -34377,7 +34379,7 @@
       </c>
       <c r="T233" s="6"/>
     </row>
-    <row r="234" spans="1:20" ht="18">
+    <row r="234" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A234" s="3" t="s">
         <v>494</v>
       </c>
@@ -34435,7 +34437,7 @@
       </c>
       <c r="T234" s="6"/>
     </row>
-    <row r="235" spans="1:20" ht="18">
+    <row r="235" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A235" s="7" t="s">
         <v>495</v>
       </c>
@@ -34493,7 +34495,7 @@
       </c>
       <c r="T235" s="6"/>
     </row>
-    <row r="236" spans="1:20" ht="18">
+    <row r="236" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A236" s="3" t="s">
         <v>497</v>
       </c>
@@ -34551,7 +34553,7 @@
       </c>
       <c r="T236" s="6"/>
     </row>
-    <row r="237" spans="1:20" ht="18">
+    <row r="237" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A237" s="7" t="s">
         <v>500</v>
       </c>
@@ -34609,7 +34611,7 @@
       </c>
       <c r="T237" s="6"/>
     </row>
-    <row r="238" spans="1:20" ht="18">
+    <row r="238" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A238" s="3" t="s">
         <v>501</v>
       </c>
@@ -34667,7 +34669,7 @@
       </c>
       <c r="T238" s="6"/>
     </row>
-    <row r="239" spans="1:20" ht="18">
+    <row r="239" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A239" s="7" t="s">
         <v>502</v>
       </c>
@@ -34725,7 +34727,7 @@
       </c>
       <c r="T239" s="6"/>
     </row>
-    <row r="240" spans="1:20" ht="18">
+    <row r="240" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A240" s="3" t="s">
         <v>505</v>
       </c>
@@ -34783,7 +34785,7 @@
       </c>
       <c r="T240" s="6"/>
     </row>
-    <row r="241" spans="1:20" ht="18">
+    <row r="241" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A241" s="7" t="s">
         <v>509</v>
       </c>
@@ -34841,7 +34843,7 @@
       </c>
       <c r="T241" s="6"/>
     </row>
-    <row r="242" spans="1:20" ht="18">
+    <row r="242" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A242" s="3" t="s">
         <v>512</v>
       </c>
@@ -34899,7 +34901,7 @@
       </c>
       <c r="T242" s="6"/>
     </row>
-    <row r="243" spans="1:20" ht="18">
+    <row r="243" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A243" s="7" t="s">
         <v>513</v>
       </c>
@@ -34957,7 +34959,7 @@
       </c>
       <c r="T243" s="6"/>
     </row>
-    <row r="244" spans="1:20" ht="18">
+    <row r="244" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A244" s="3" t="s">
         <v>516</v>
       </c>
@@ -35015,7 +35017,7 @@
       </c>
       <c r="T244" s="6"/>
     </row>
-    <row r="245" spans="1:20" ht="18">
+    <row r="245" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A245" s="7" t="s">
         <v>517</v>
       </c>
@@ -35073,7 +35075,7 @@
       </c>
       <c r="T245" s="6"/>
     </row>
-    <row r="246" spans="1:20" ht="18">
+    <row r="246" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A246" s="3" t="s">
         <v>521</v>
       </c>
@@ -35131,7 +35133,7 @@
       </c>
       <c r="T246" s="6"/>
     </row>
-    <row r="247" spans="1:20" ht="18">
+    <row r="247" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A247" s="7" t="s">
         <v>523</v>
       </c>
@@ -35189,7 +35191,7 @@
       </c>
       <c r="T247" s="6"/>
     </row>
-    <row r="248" spans="1:20" ht="18">
+    <row r="248" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A248" s="3" t="s">
         <v>524</v>
       </c>
@@ -35247,7 +35249,7 @@
       </c>
       <c r="T248" s="6"/>
     </row>
-    <row r="249" spans="1:20" ht="18">
+    <row r="249" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A249" s="7" t="s">
         <v>528</v>
       </c>
@@ -35305,7 +35307,7 @@
       </c>
       <c r="T249" s="6"/>
     </row>
-    <row r="250" spans="1:20" ht="18">
+    <row r="250" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A250" s="3" t="s">
         <v>529</v>
       </c>
@@ -35363,7 +35365,7 @@
       </c>
       <c r="T250" s="6"/>
     </row>
-    <row r="251" spans="1:20" ht="18">
+    <row r="251" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A251" s="7" t="s">
         <v>530</v>
       </c>
@@ -35421,7 +35423,7 @@
       </c>
       <c r="T251" s="6"/>
     </row>
-    <row r="252" spans="1:20" ht="18">
+    <row r="252" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A252" s="3" t="s">
         <v>533</v>
       </c>
@@ -35479,7 +35481,7 @@
       </c>
       <c r="T252" s="6"/>
     </row>
-    <row r="253" spans="1:20" ht="18">
+    <row r="253" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A253" s="7" t="s">
         <v>534</v>
       </c>
@@ -35537,7 +35539,7 @@
       </c>
       <c r="T253" s="6"/>
     </row>
-    <row r="254" spans="1:20" ht="18">
+    <row r="254" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A254" s="3" t="s">
         <v>536</v>
       </c>
@@ -35595,7 +35597,7 @@
       </c>
       <c r="T254" s="6"/>
     </row>
-    <row r="255" spans="1:20" ht="18">
+    <row r="255" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A255" s="7" t="s">
         <v>540</v>
       </c>
@@ -35653,7 +35655,7 @@
       </c>
       <c r="T255" s="6"/>
     </row>
-    <row r="256" spans="1:20" ht="18">
+    <row r="256" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A256" s="3" t="s">
         <v>541</v>
       </c>
@@ -35711,7 +35713,7 @@
       </c>
       <c r="T256" s="6"/>
     </row>
-    <row r="257" spans="1:20" ht="18">
+    <row r="257" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A257" s="7" t="s">
         <v>545</v>
       </c>
@@ -35769,7 +35771,7 @@
       </c>
       <c r="T257" s="6"/>
     </row>
-    <row r="258" spans="1:20" ht="18">
+    <row r="258" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A258" s="3" t="s">
         <v>549</v>
       </c>
@@ -35827,7 +35829,7 @@
       </c>
       <c r="T258" s="6"/>
     </row>
-    <row r="259" spans="1:20" ht="18">
+    <row r="259" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A259" s="7" t="s">
         <v>550</v>
       </c>
@@ -35885,7 +35887,7 @@
       </c>
       <c r="T259" s="6"/>
     </row>
-    <row r="260" spans="1:20" ht="18">
+    <row r="260" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A260" s="3" t="s">
         <v>551</v>
       </c>
@@ -35943,7 +35945,7 @@
       </c>
       <c r="T260" s="6"/>
     </row>
-    <row r="261" spans="1:20" ht="18">
+    <row r="261" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A261" s="7" t="s">
         <v>554</v>
       </c>
@@ -36001,7 +36003,7 @@
       </c>
       <c r="T261" s="6"/>
     </row>
-    <row r="262" spans="1:20" ht="18">
+    <row r="262" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A262" s="3" t="s">
         <v>555</v>
       </c>
@@ -36059,7 +36061,7 @@
       </c>
       <c r="T262" s="6"/>
     </row>
-    <row r="263" spans="1:20" ht="18">
+    <row r="263" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A263" s="7" t="s">
         <v>556</v>
       </c>
@@ -36117,7 +36119,7 @@
       </c>
       <c r="T263" s="6"/>
     </row>
-    <row r="264" spans="1:20" ht="18">
+    <row r="264" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A264" s="3" t="s">
         <v>557</v>
       </c>
@@ -36175,7 +36177,7 @@
       </c>
       <c r="T264" s="6"/>
     </row>
-    <row r="265" spans="1:20" ht="18">
+    <row r="265" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A265" s="7" t="s">
         <v>559</v>
       </c>
@@ -36233,7 +36235,7 @@
       </c>
       <c r="T265" s="6"/>
     </row>
-    <row r="266" spans="1:20" ht="18">
+    <row r="266" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A266" s="3" t="s">
         <v>561</v>
       </c>
@@ -36293,7 +36295,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="267" spans="1:20" ht="18">
+    <row r="267" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A267" s="7" t="s">
         <v>562</v>
       </c>
@@ -36351,7 +36353,7 @@
       </c>
       <c r="T267" s="6"/>
     </row>
-    <row r="268" spans="1:20" ht="18">
+    <row r="268" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A268" s="3" t="s">
         <v>563</v>
       </c>
@@ -36409,7 +36411,7 @@
       </c>
       <c r="T268" s="6"/>
     </row>
-    <row r="269" spans="1:20" ht="18">
+    <row r="269" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A269" s="7" t="s">
         <v>567</v>
       </c>
@@ -36467,7 +36469,7 @@
       </c>
       <c r="T269" s="6"/>
     </row>
-    <row r="270" spans="1:20" ht="18">
+    <row r="270" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A270" s="3" t="s">
         <v>571</v>
       </c>
@@ -36525,7 +36527,7 @@
       </c>
       <c r="T270" s="6"/>
     </row>
-    <row r="271" spans="1:20" ht="18">
+    <row r="271" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A271" s="7" t="s">
         <v>572</v>
       </c>
@@ -36583,7 +36585,7 @@
       </c>
       <c r="T271" s="6"/>
     </row>
-    <row r="272" spans="1:20" ht="18">
+    <row r="272" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A272" s="3" t="s">
         <v>573</v>
       </c>
@@ -36641,7 +36643,7 @@
       </c>
       <c r="T272" s="6"/>
     </row>
-    <row r="273" spans="1:20" ht="18">
+    <row r="273" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A273" s="7" t="s">
         <v>575</v>
       </c>
@@ -36699,7 +36701,7 @@
       </c>
       <c r="T273" s="6"/>
     </row>
-    <row r="274" spans="1:20" ht="18">
+    <row r="274" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A274" s="3" t="s">
         <v>577</v>
       </c>
@@ -36757,7 +36759,7 @@
       </c>
       <c r="T274" s="6"/>
     </row>
-    <row r="275" spans="1:20" ht="18">
+    <row r="275" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A275" s="7" t="s">
         <v>579</v>
       </c>
@@ -36815,7 +36817,7 @@
       </c>
       <c r="T275" s="6"/>
     </row>
-    <row r="276" spans="1:20" ht="18">
+    <row r="276" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A276" s="3" t="s">
         <v>581</v>
       </c>
@@ -36873,7 +36875,7 @@
       </c>
       <c r="T276" s="6"/>
     </row>
-    <row r="277" spans="1:20" ht="18">
+    <row r="277" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A277" s="7" t="s">
         <v>583</v>
       </c>
@@ -36931,7 +36933,7 @@
       </c>
       <c r="T277" s="6"/>
     </row>
-    <row r="278" spans="1:20" ht="18">
+    <row r="278" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A278" s="3" t="s">
         <v>584</v>
       </c>
@@ -36989,7 +36991,7 @@
       </c>
       <c r="T278" s="6"/>
     </row>
-    <row r="279" spans="1:20" ht="18">
+    <row r="279" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A279" s="7" t="s">
         <v>586</v>
       </c>
@@ -37047,7 +37049,7 @@
       </c>
       <c r="T279" s="6"/>
     </row>
-    <row r="280" spans="1:20" ht="18">
+    <row r="280" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A280" s="3" t="s">
         <v>587</v>
       </c>
@@ -37105,7 +37107,7 @@
       </c>
       <c r="T280" s="6"/>
     </row>
-    <row r="281" spans="1:20" ht="18">
+    <row r="281" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A281" s="7" t="s">
         <v>589</v>
       </c>
@@ -37163,7 +37165,7 @@
       </c>
       <c r="T281" s="6"/>
     </row>
-    <row r="282" spans="1:20" ht="18">
+    <row r="282" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A282" s="3" t="s">
         <v>590</v>
       </c>
@@ -37221,7 +37223,7 @@
       </c>
       <c r="T282" s="6"/>
     </row>
-    <row r="283" spans="1:20" ht="18">
+    <row r="283" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A283" s="7" t="s">
         <v>594</v>
       </c>
@@ -37279,7 +37281,7 @@
       </c>
       <c r="T283" s="6"/>
     </row>
-    <row r="284" spans="1:20" ht="18">
+    <row r="284" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A284" s="3" t="s">
         <v>595</v>
       </c>
@@ -37337,7 +37339,7 @@
       </c>
       <c r="T284" s="6"/>
     </row>
-    <row r="285" spans="1:20" ht="18">
+    <row r="285" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A285" s="7" t="s">
         <v>597</v>
       </c>
@@ -37395,7 +37397,7 @@
       </c>
       <c r="T285" s="6"/>
     </row>
-    <row r="286" spans="1:20" ht="18">
+    <row r="286" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A286" s="3" t="s">
         <v>599</v>
       </c>
@@ -37453,7 +37455,7 @@
       </c>
       <c r="T286" s="6"/>
     </row>
-    <row r="287" spans="1:20" ht="18">
+    <row r="287" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A287" s="7" t="s">
         <v>600</v>
       </c>
@@ -37511,7 +37513,7 @@
       </c>
       <c r="T287" s="6"/>
     </row>
-    <row r="288" spans="1:20" ht="18">
+    <row r="288" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A288" s="3" t="s">
         <v>602</v>
       </c>
@@ -37569,7 +37571,7 @@
       </c>
       <c r="T288" s="6"/>
     </row>
-    <row r="289" spans="1:20" ht="18">
+    <row r="289" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A289" s="7" t="s">
         <v>604</v>
       </c>
@@ -37627,7 +37629,7 @@
       </c>
       <c r="T289" s="6"/>
     </row>
-    <row r="290" spans="1:20" ht="18">
+    <row r="290" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A290" s="3" t="s">
         <v>606</v>
       </c>
@@ -37685,7 +37687,7 @@
       </c>
       <c r="T290" s="6"/>
     </row>
-    <row r="291" spans="1:20" ht="18">
+    <row r="291" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A291" s="7" t="s">
         <v>607</v>
       </c>
@@ -37743,7 +37745,7 @@
       </c>
       <c r="T291" s="6"/>
     </row>
-    <row r="292" spans="1:20" ht="18">
+    <row r="292" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A292" s="3" t="s">
         <v>608</v>
       </c>
@@ -37801,7 +37803,7 @@
       </c>
       <c r="T292" s="6"/>
     </row>
-    <row r="293" spans="1:20" ht="18">
+    <row r="293" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A293" s="7" t="s">
         <v>609</v>
       </c>
@@ -37859,7 +37861,7 @@
       </c>
       <c r="T293" s="6"/>
     </row>
-    <row r="294" spans="1:20" ht="18">
+    <row r="294" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A294" s="3" t="s">
         <v>611</v>
       </c>
@@ -37917,7 +37919,7 @@
       </c>
       <c r="T294" s="6"/>
     </row>
-    <row r="295" spans="1:20" ht="18">
+    <row r="295" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A295" s="7" t="s">
         <v>612</v>
       </c>
@@ -37975,7 +37977,7 @@
       </c>
       <c r="T295" s="6"/>
     </row>
-    <row r="296" spans="1:20" ht="18">
+    <row r="296" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A296" s="3" t="s">
         <v>614</v>
       </c>
@@ -38033,7 +38035,7 @@
       </c>
       <c r="T296" s="6"/>
     </row>
-    <row r="297" spans="1:20" ht="18">
+    <row r="297" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A297" s="7" t="s">
         <v>615</v>
       </c>
@@ -38091,7 +38093,7 @@
       </c>
       <c r="T297" s="6"/>
     </row>
-    <row r="298" spans="1:20" ht="18">
+    <row r="298" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A298" s="3" t="s">
         <v>617</v>
       </c>
@@ -38149,7 +38151,7 @@
       </c>
       <c r="T298" s="6"/>
     </row>
-    <row r="299" spans="1:20" ht="18">
+    <row r="299" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A299" s="7" t="s">
         <v>618</v>
       </c>
@@ -38207,7 +38209,7 @@
       </c>
       <c r="T299" s="6"/>
     </row>
-    <row r="300" spans="1:20" ht="18">
+    <row r="300" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A300" s="3" t="s">
         <v>620</v>
       </c>
@@ -38265,7 +38267,7 @@
       </c>
       <c r="T300" s="6"/>
     </row>
-    <row r="301" spans="1:20" ht="18">
+    <row r="301" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A301" s="7" t="s">
         <v>622</v>
       </c>
@@ -38323,7 +38325,7 @@
       </c>
       <c r="T301" s="6"/>
     </row>
-    <row r="302" spans="1:20" ht="18">
+    <row r="302" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A302" s="3" t="s">
         <v>623</v>
       </c>
@@ -38381,7 +38383,7 @@
       </c>
       <c r="T302" s="6"/>
     </row>
-    <row r="303" spans="1:20" ht="18">
+    <row r="303" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A303" s="7" t="s">
         <v>625</v>
       </c>
@@ -38439,7 +38441,7 @@
       </c>
       <c r="T303" s="6"/>
     </row>
-    <row r="304" spans="1:20" ht="18">
+    <row r="304" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A304" s="3" t="s">
         <v>626</v>
       </c>
@@ -38497,7 +38499,7 @@
       </c>
       <c r="T304" s="6"/>
     </row>
-    <row r="305" spans="1:20" ht="18">
+    <row r="305" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A305" s="7" t="s">
         <v>629</v>
       </c>
@@ -38555,7 +38557,7 @@
       </c>
       <c r="T305" s="6"/>
     </row>
-    <row r="306" spans="1:20" ht="18">
+    <row r="306" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A306" s="3" t="s">
         <v>631</v>
       </c>
@@ -38613,7 +38615,7 @@
       </c>
       <c r="T306" s="6"/>
     </row>
-    <row r="307" spans="1:20" ht="18">
+    <row r="307" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A307" s="7" t="s">
         <v>632</v>
       </c>
@@ -38667,7 +38669,7 @@
       </c>
       <c r="T307" s="6"/>
     </row>
-    <row r="308" spans="1:20" ht="18">
+    <row r="308" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A308" s="3" t="s">
         <v>636</v>
       </c>
@@ -38725,7 +38727,7 @@
       </c>
       <c r="T308" s="6"/>
     </row>
-    <row r="309" spans="1:20" ht="18">
+    <row r="309" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A309" s="7" t="s">
         <v>637</v>
       </c>
@@ -38783,7 +38785,7 @@
       </c>
       <c r="T309" s="6"/>
     </row>
-    <row r="310" spans="1:20" ht="18">
+    <row r="310" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A310" s="3" t="s">
         <v>638</v>
       </c>
@@ -38841,7 +38843,7 @@
       </c>
       <c r="T310" s="6"/>
     </row>
-    <row r="311" spans="1:20" ht="18">
+    <row r="311" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A311" s="7" t="s">
         <v>640</v>
       </c>
@@ -38899,7 +38901,7 @@
       </c>
       <c r="T311" s="6"/>
     </row>
-    <row r="312" spans="1:20" ht="18">
+    <row r="312" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A312" s="3" t="s">
         <v>641</v>
       </c>
@@ -38957,7 +38959,7 @@
       </c>
       <c r="T312" s="6"/>
     </row>
-    <row r="313" spans="1:20" ht="18">
+    <row r="313" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A313" s="7" t="s">
         <v>643</v>
       </c>
@@ -39015,7 +39017,7 @@
       </c>
       <c r="T313" s="6"/>
     </row>
-    <row r="314" spans="1:20" ht="18">
+    <row r="314" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A314" s="3" t="s">
         <v>645</v>
       </c>
@@ -39073,7 +39075,7 @@
       </c>
       <c r="T314" s="6"/>
     </row>
-    <row r="315" spans="1:20" ht="18">
+    <row r="315" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A315" s="7" t="s">
         <v>648</v>
       </c>
@@ -39131,7 +39133,7 @@
       </c>
       <c r="T315" s="6"/>
     </row>
-    <row r="316" spans="1:20" ht="18">
+    <row r="316" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A316" s="3" t="s">
         <v>649</v>
       </c>
@@ -39189,7 +39191,7 @@
       </c>
       <c r="T316" s="6"/>
     </row>
-    <row r="317" spans="1:20" ht="18">
+    <row r="317" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A317" s="7" t="s">
         <v>650</v>
       </c>
@@ -39247,7 +39249,7 @@
       </c>
       <c r="T317" s="6"/>
     </row>
-    <row r="318" spans="1:20" ht="18">
+    <row r="318" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A318" s="3" t="s">
         <v>651</v>
       </c>
@@ -39305,7 +39307,7 @@
       </c>
       <c r="T318" s="6"/>
     </row>
-    <row r="319" spans="1:20" ht="18">
+    <row r="319" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A319" s="7" t="s">
         <v>652</v>
       </c>
@@ -39365,7 +39367,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="320" spans="1:20" ht="18">
+    <row r="320" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A320" s="3" t="s">
         <v>653</v>
       </c>
@@ -39425,7 +39427,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="321" spans="1:20" ht="18">
+    <row r="321" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A321" s="7" t="s">
         <v>655</v>
       </c>
@@ -39483,7 +39485,7 @@
       </c>
       <c r="T321" s="6"/>
     </row>
-    <row r="322" spans="1:20" ht="18">
+    <row r="322" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A322" s="3" t="s">
         <v>657</v>
       </c>
@@ -39541,7 +39543,7 @@
       </c>
       <c r="T322" s="6"/>
     </row>
-    <row r="323" spans="1:20" ht="18">
+    <row r="323" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A323" s="7" t="s">
         <v>661</v>
       </c>
@@ -39599,7 +39601,7 @@
       </c>
       <c r="T323" s="6"/>
     </row>
-    <row r="324" spans="1:20" ht="18">
+    <row r="324" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A324" s="3" t="s">
         <v>662</v>
       </c>
@@ -39657,7 +39659,7 @@
       </c>
       <c r="T324" s="6"/>
     </row>
-    <row r="325" spans="1:20" ht="18">
+    <row r="325" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A325" s="7" t="s">
         <v>663</v>
       </c>
@@ -39715,7 +39717,7 @@
       </c>
       <c r="T325" s="6"/>
     </row>
-    <row r="326" spans="1:20" ht="18">
+    <row r="326" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A326" s="3" t="s">
         <v>664</v>
       </c>
@@ -39773,7 +39775,7 @@
       </c>
       <c r="T326" s="6"/>
     </row>
-    <row r="327" spans="1:20" ht="18">
+    <row r="327" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A327" s="7" t="s">
         <v>667</v>
       </c>
@@ -39831,7 +39833,7 @@
       </c>
       <c r="T327" s="6"/>
     </row>
-    <row r="328" spans="1:20" ht="18">
+    <row r="328" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A328" s="3" t="s">
         <v>668</v>
       </c>
@@ -39889,7 +39891,7 @@
       </c>
       <c r="T328" s="6"/>
     </row>
-    <row r="329" spans="1:20" ht="18">
+    <row r="329" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A329" s="7" t="s">
         <v>669</v>
       </c>
@@ -39947,7 +39949,7 @@
       </c>
       <c r="T329" s="6"/>
     </row>
-    <row r="330" spans="1:20" ht="18">
+    <row r="330" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A330" s="3" t="s">
         <v>670</v>
       </c>
@@ -40005,7 +40007,7 @@
       </c>
       <c r="T330" s="6"/>
     </row>
-    <row r="331" spans="1:20" ht="18">
+    <row r="331" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A331" s="7" t="s">
         <v>672</v>
       </c>
@@ -40063,7 +40065,7 @@
       </c>
       <c r="T331" s="6"/>
     </row>
-    <row r="332" spans="1:20" ht="18">
+    <row r="332" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A332" s="3" t="s">
         <v>673</v>
       </c>
@@ -40119,7 +40121,7 @@
       </c>
       <c r="T332" s="6"/>
     </row>
-    <row r="333" spans="1:20" ht="18">
+    <row r="333" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A333" s="7" t="s">
         <v>675</v>
       </c>
@@ -40177,7 +40179,7 @@
       </c>
       <c r="T333" s="6"/>
     </row>
-    <row r="334" spans="1:20" ht="18">
+    <row r="334" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A334" s="3" t="s">
         <v>676</v>
       </c>
@@ -40231,7 +40233,7 @@
       </c>
       <c r="T334" s="6"/>
     </row>
-    <row r="335" spans="1:20" ht="18">
+    <row r="335" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A335" s="7" t="s">
         <v>677</v>
       </c>
@@ -40289,7 +40291,7 @@
       </c>
       <c r="T335" s="6"/>
     </row>
-    <row r="336" spans="1:20" ht="18">
+    <row r="336" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A336" s="3" t="s">
         <v>679</v>
       </c>
@@ -40347,7 +40349,7 @@
       </c>
       <c r="T336" s="6"/>
     </row>
-    <row r="337" spans="1:20" ht="18">
+    <row r="337" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A337" s="7" t="s">
         <v>682</v>
       </c>
@@ -40405,7 +40407,7 @@
       </c>
       <c r="T337" s="6"/>
     </row>
-    <row r="338" spans="1:20" ht="18">
+    <row r="338" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A338" s="3" t="s">
         <v>683</v>
       </c>
@@ -40463,7 +40465,7 @@
       </c>
       <c r="T338" s="6"/>
     </row>
-    <row r="339" spans="1:20" ht="18">
+    <row r="339" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A339" s="7" t="s">
         <v>687</v>
       </c>
@@ -40521,7 +40523,7 @@
       </c>
       <c r="T339" s="6"/>
     </row>
-    <row r="340" spans="1:20" ht="18">
+    <row r="340" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A340" s="3" t="s">
         <v>689</v>
       </c>
@@ -40579,7 +40581,7 @@
       </c>
       <c r="T340" s="6"/>
     </row>
-    <row r="341" spans="1:20" ht="18">
+    <row r="341" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A341" s="7" t="s">
         <v>690</v>
       </c>
@@ -40637,7 +40639,7 @@
       </c>
       <c r="T341" s="6"/>
     </row>
-    <row r="342" spans="1:20" ht="18">
+    <row r="342" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A342" s="3" t="s">
         <v>694</v>
       </c>
@@ -40695,7 +40697,7 @@
       </c>
       <c r="T342" s="6"/>
     </row>
-    <row r="343" spans="1:20" ht="18">
+    <row r="343" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A343" s="7" t="s">
         <v>695</v>
       </c>
@@ -40753,7 +40755,7 @@
       </c>
       <c r="T343" s="6"/>
     </row>
-    <row r="344" spans="1:20" ht="18">
+    <row r="344" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A344" s="3" t="s">
         <v>697</v>
       </c>
@@ -40811,7 +40813,7 @@
       </c>
       <c r="T344" s="6"/>
     </row>
-    <row r="345" spans="1:20" ht="18">
+    <row r="345" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A345" s="7" t="s">
         <v>698</v>
       </c>
@@ -40869,7 +40871,7 @@
       </c>
       <c r="T345" s="6"/>
     </row>
-    <row r="346" spans="1:20" ht="18">
+    <row r="346" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A346" s="3" t="s">
         <v>700</v>
       </c>
@@ -40927,7 +40929,7 @@
       </c>
       <c r="T346" s="6"/>
     </row>
-    <row r="347" spans="1:20" ht="18">
+    <row r="347" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A347" s="7" t="s">
         <v>701</v>
       </c>
@@ -40985,7 +40987,7 @@
       </c>
       <c r="T347" s="6"/>
     </row>
-    <row r="348" spans="1:20" ht="18">
+    <row r="348" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A348" s="3" t="s">
         <v>703</v>
       </c>
@@ -41043,7 +41045,7 @@
       </c>
       <c r="T348" s="6"/>
     </row>
-    <row r="349" spans="1:20" ht="18">
+    <row r="349" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A349" s="7" t="s">
         <v>704</v>
       </c>
@@ -41101,7 +41103,7 @@
       </c>
       <c r="T349" s="6"/>
     </row>
-    <row r="350" spans="1:20" ht="18">
+    <row r="350" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A350" s="3" t="s">
         <v>705</v>
       </c>
@@ -41159,7 +41161,7 @@
       </c>
       <c r="T350" s="6"/>
     </row>
-    <row r="351" spans="1:20" ht="18">
+    <row r="351" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A351" s="7" t="s">
         <v>707</v>
       </c>
@@ -41217,7 +41219,7 @@
       </c>
       <c r="T351" s="6"/>
     </row>
-    <row r="352" spans="1:20" ht="18">
+    <row r="352" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A352" s="3" t="s">
         <v>708</v>
       </c>
@@ -41275,7 +41277,7 @@
       </c>
       <c r="T352" s="6"/>
     </row>
-    <row r="353" spans="1:20" ht="18">
+    <row r="353" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A353" s="7" t="s">
         <v>711</v>
       </c>
@@ -41333,7 +41335,7 @@
       </c>
       <c r="T353" s="6"/>
     </row>
-    <row r="354" spans="1:20" ht="18">
+    <row r="354" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A354" s="3" t="s">
         <v>712</v>
       </c>
@@ -41391,7 +41393,7 @@
       </c>
       <c r="T354" s="6"/>
     </row>
-    <row r="355" spans="1:20" ht="18">
+    <row r="355" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A355" s="7" t="s">
         <v>714</v>
       </c>
@@ -41449,7 +41451,7 @@
       </c>
       <c r="T355" s="6"/>
     </row>
-    <row r="356" spans="1:20" ht="18">
+    <row r="356" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A356" s="3" t="s">
         <v>716</v>
       </c>
@@ -41507,7 +41509,7 @@
       </c>
       <c r="T356" s="6"/>
     </row>
-    <row r="357" spans="1:20" ht="18">
+    <row r="357" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A357" s="7" t="s">
         <v>718</v>
       </c>
@@ -41565,7 +41567,7 @@
       </c>
       <c r="T357" s="6"/>
     </row>
-    <row r="358" spans="1:20" ht="18">
+    <row r="358" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A358" s="3" t="s">
         <v>720</v>
       </c>
@@ -41623,7 +41625,7 @@
       </c>
       <c r="T358" s="6"/>
     </row>
-    <row r="359" spans="1:20" ht="18">
+    <row r="359" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A359" s="7" t="s">
         <v>722</v>
       </c>
@@ -41681,7 +41683,7 @@
       </c>
       <c r="T359" s="6"/>
     </row>
-    <row r="360" spans="1:20" ht="18">
+    <row r="360" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A360" s="3" t="s">
         <v>724</v>
       </c>
@@ -41739,7 +41741,7 @@
       </c>
       <c r="T360" s="6"/>
     </row>
-    <row r="361" spans="1:20" ht="18">
+    <row r="361" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A361" s="7" t="s">
         <v>725</v>
       </c>
@@ -41797,7 +41799,7 @@
       </c>
       <c r="T361" s="6"/>
     </row>
-    <row r="362" spans="1:20" ht="18">
+    <row r="362" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A362" s="3" t="s">
         <v>727</v>
       </c>
@@ -41855,7 +41857,7 @@
       </c>
       <c r="T362" s="6"/>
     </row>
-    <row r="363" spans="1:20" ht="18">
+    <row r="363" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A363" s="7" t="s">
         <v>728</v>
       </c>
@@ -41913,7 +41915,7 @@
       </c>
       <c r="T363" s="6"/>
     </row>
-    <row r="364" spans="1:20" ht="18">
+    <row r="364" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A364" s="3" t="s">
         <v>730</v>
       </c>
@@ -41971,7 +41973,7 @@
       </c>
       <c r="T364" s="6"/>
     </row>
-    <row r="365" spans="1:20" ht="18">
+    <row r="365" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A365" s="7" t="s">
         <v>732</v>
       </c>
@@ -42031,7 +42033,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="366" spans="1:20" ht="18">
+    <row r="366" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A366" s="3" t="s">
         <v>733</v>
       </c>
@@ -42089,7 +42091,7 @@
       </c>
       <c r="T366" s="6"/>
     </row>
-    <row r="367" spans="1:20" ht="18">
+    <row r="367" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A367" s="7" t="s">
         <v>734</v>
       </c>
@@ -42147,7 +42149,7 @@
       </c>
       <c r="T367" s="6"/>
     </row>
-    <row r="368" spans="1:20" ht="18">
+    <row r="368" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A368" s="3" t="s">
         <v>735</v>
       </c>
@@ -42205,7 +42207,7 @@
       </c>
       <c r="T368" s="6"/>
     </row>
-    <row r="369" spans="1:20" ht="18">
+    <row r="369" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A369" s="7" t="s">
         <v>736</v>
       </c>
@@ -42263,7 +42265,7 @@
       </c>
       <c r="T369" s="6"/>
     </row>
-    <row r="370" spans="1:20" ht="18">
+    <row r="370" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A370" s="3" t="s">
         <v>737</v>
       </c>
@@ -42323,7 +42325,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="371" spans="1:20" ht="18">
+    <row r="371" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A371" s="7" t="s">
         <v>738</v>
       </c>
@@ -42381,7 +42383,7 @@
       </c>
       <c r="T371" s="6"/>
     </row>
-    <row r="372" spans="1:20" ht="18">
+    <row r="372" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A372" s="3" t="s">
         <v>739</v>
       </c>
@@ -42439,7 +42441,7 @@
       </c>
       <c r="T372" s="6"/>
     </row>
-    <row r="373" spans="1:20" ht="18">
+    <row r="373" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A373" s="7" t="s">
         <v>740</v>
       </c>
@@ -42497,7 +42499,7 @@
       </c>
       <c r="T373" s="6"/>
     </row>
-    <row r="374" spans="1:20" ht="18">
+    <row r="374" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A374" s="3" t="s">
         <v>741</v>
       </c>
@@ -42555,7 +42557,7 @@
       </c>
       <c r="T374" s="6"/>
     </row>
-    <row r="375" spans="1:20" ht="18">
+    <row r="375" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A375" s="7" t="s">
         <v>742</v>
       </c>
@@ -42613,7 +42615,7 @@
       </c>
       <c r="T375" s="6"/>
     </row>
-    <row r="376" spans="1:20" ht="18">
+    <row r="376" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A376" s="3" t="s">
         <v>744</v>
       </c>
@@ -42671,7 +42673,7 @@
       </c>
       <c r="T376" s="6"/>
     </row>
-    <row r="377" spans="1:20" ht="18">
+    <row r="377" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A377" s="7" t="s">
         <v>747</v>
       </c>
@@ -42729,7 +42731,7 @@
       </c>
       <c r="T377" s="6"/>
     </row>
-    <row r="378" spans="1:20" ht="18">
+    <row r="378" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A378" s="3" t="s">
         <v>748</v>
       </c>
@@ -42787,7 +42789,7 @@
       </c>
       <c r="T378" s="6"/>
     </row>
-    <row r="379" spans="1:20" ht="18">
+    <row r="379" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A379" s="7" t="s">
         <v>749</v>
       </c>
@@ -42845,7 +42847,7 @@
       </c>
       <c r="T379" s="6"/>
     </row>
-    <row r="380" spans="1:20" ht="18">
+    <row r="380" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A380" s="3" t="s">
         <v>751</v>
       </c>
@@ -42903,7 +42905,7 @@
       </c>
       <c r="T380" s="6"/>
     </row>
-    <row r="381" spans="1:20" ht="18">
+    <row r="381" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A381" s="7" t="s">
         <v>752</v>
       </c>
@@ -42961,7 +42963,7 @@
       </c>
       <c r="T381" s="6"/>
     </row>
-    <row r="382" spans="1:20" ht="18">
+    <row r="382" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A382" s="3" t="s">
         <v>753</v>
       </c>
@@ -43019,7 +43021,7 @@
       </c>
       <c r="T382" s="6"/>
     </row>
-    <row r="383" spans="1:20" ht="18">
+    <row r="383" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A383" s="7" t="s">
         <v>754</v>
       </c>
@@ -43073,7 +43075,7 @@
       </c>
       <c r="T383" s="6"/>
     </row>
-    <row r="384" spans="1:20" ht="18">
+    <row r="384" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A384" s="3" t="s">
         <v>755</v>
       </c>
@@ -43131,7 +43133,7 @@
       </c>
       <c r="T384" s="6"/>
     </row>
-    <row r="385" spans="1:20" ht="18">
+    <row r="385" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A385" s="7" t="s">
         <v>756</v>
       </c>
@@ -43189,7 +43191,7 @@
       </c>
       <c r="T385" s="6"/>
     </row>
-    <row r="386" spans="1:20" ht="18">
+    <row r="386" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A386" s="3" t="s">
         <v>757</v>
       </c>
@@ -43247,7 +43249,7 @@
       </c>
       <c r="T386" s="6"/>
     </row>
-    <row r="387" spans="1:20" ht="18">
+    <row r="387" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A387" s="7" t="s">
         <v>758</v>
       </c>
@@ -43305,7 +43307,7 @@
       </c>
       <c r="T387" s="6"/>
     </row>
-    <row r="388" spans="1:20" ht="18">
+    <row r="388" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A388" s="3" t="s">
         <v>760</v>
       </c>
@@ -43363,7 +43365,7 @@
       </c>
       <c r="T388" s="6"/>
     </row>
-    <row r="389" spans="1:20" ht="18">
+    <row r="389" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A389" s="7" t="s">
         <v>761</v>
       </c>
@@ -43421,7 +43423,7 @@
       </c>
       <c r="T389" s="6"/>
     </row>
-    <row r="390" spans="1:20" ht="18">
+    <row r="390" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A390" s="3" t="s">
         <v>762</v>
       </c>
@@ -43479,7 +43481,7 @@
       </c>
       <c r="T390" s="6"/>
     </row>
-    <row r="391" spans="1:20" ht="18">
+    <row r="391" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A391" s="7" t="s">
         <v>763</v>
       </c>
@@ -43537,7 +43539,7 @@
       </c>
       <c r="T391" s="6"/>
     </row>
-    <row r="392" spans="1:20" ht="18">
+    <row r="392" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A392" s="3" t="s">
         <v>764</v>
       </c>
@@ -43595,7 +43597,7 @@
       </c>
       <c r="T392" s="6"/>
     </row>
-    <row r="393" spans="1:20" ht="18">
+    <row r="393" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A393" s="7" t="s">
         <v>765</v>
       </c>
@@ -43653,7 +43655,7 @@
       </c>
       <c r="T393" s="6"/>
     </row>
-    <row r="394" spans="1:20" ht="18">
+    <row r="394" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A394" s="3" t="s">
         <v>766</v>
       </c>
@@ -43711,7 +43713,7 @@
       </c>
       <c r="T394" s="6"/>
     </row>
-    <row r="395" spans="1:20" ht="18">
+    <row r="395" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A395" s="7" t="s">
         <v>767</v>
       </c>
@@ -43769,7 +43771,7 @@
       </c>
       <c r="T395" s="6"/>
     </row>
-    <row r="396" spans="1:20" ht="18">
+    <row r="396" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A396" s="3" t="s">
         <v>769</v>
       </c>
@@ -43827,7 +43829,7 @@
       </c>
       <c r="T396" s="6"/>
     </row>
-    <row r="397" spans="1:20" ht="18">
+    <row r="397" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A397" s="7" t="s">
         <v>770</v>
       </c>
@@ -43885,7 +43887,7 @@
       </c>
       <c r="T397" s="6"/>
     </row>
-    <row r="398" spans="1:20" ht="18">
+    <row r="398" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A398" s="3" t="s">
         <v>772</v>
       </c>
@@ -43943,7 +43945,7 @@
       </c>
       <c r="T398" s="6"/>
     </row>
-    <row r="399" spans="1:20" ht="18">
+    <row r="399" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A399" s="7" t="s">
         <v>773</v>
       </c>
@@ -44001,7 +44003,7 @@
       </c>
       <c r="T399" s="6"/>
     </row>
-    <row r="400" spans="1:20" ht="18">
+    <row r="400" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A400" s="3" t="s">
         <v>775</v>
       </c>
@@ -44059,7 +44061,7 @@
       </c>
       <c r="T400" s="6"/>
     </row>
-    <row r="401" spans="1:20" ht="18">
+    <row r="401" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A401" s="7" t="s">
         <v>776</v>
       </c>
@@ -44117,7 +44119,7 @@
       </c>
       <c r="T401" s="6"/>
     </row>
-    <row r="402" spans="1:20" ht="18">
+    <row r="402" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A402" s="3" t="s">
         <v>778</v>
       </c>
@@ -44175,7 +44177,7 @@
       </c>
       <c r="T402" s="6"/>
     </row>
-    <row r="403" spans="1:20" ht="18">
+    <row r="403" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A403" s="7" t="s">
         <v>779</v>
       </c>
@@ -44233,7 +44235,7 @@
       </c>
       <c r="T403" s="6"/>
     </row>
-    <row r="404" spans="1:20" ht="18">
+    <row r="404" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A404" s="3" t="s">
         <v>781</v>
       </c>
@@ -44291,7 +44293,7 @@
       </c>
       <c r="T404" s="6"/>
     </row>
-    <row r="405" spans="1:20" ht="18">
+    <row r="405" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A405" s="7" t="s">
         <v>782</v>
       </c>
@@ -44349,7 +44351,7 @@
       </c>
       <c r="T405" s="6"/>
     </row>
-    <row r="406" spans="1:20" ht="18">
+    <row r="406" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A406" s="3" t="s">
         <v>783</v>
       </c>
@@ -44407,7 +44409,7 @@
       </c>
       <c r="T406" s="6"/>
     </row>
-    <row r="407" spans="1:20" ht="18">
+    <row r="407" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A407" s="7" t="s">
         <v>784</v>
       </c>
@@ -44465,7 +44467,7 @@
       </c>
       <c r="T407" s="6"/>
     </row>
-    <row r="408" spans="1:20" ht="18">
+    <row r="408" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A408" s="3" t="s">
         <v>785</v>
       </c>
@@ -44523,7 +44525,7 @@
       </c>
       <c r="T408" s="6"/>
     </row>
-    <row r="409" spans="1:20" ht="18">
+    <row r="409" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A409" s="7" t="s">
         <v>786</v>
       </c>
@@ -44581,7 +44583,7 @@
       </c>
       <c r="T409" s="6"/>
     </row>
-    <row r="410" spans="1:20" ht="18">
+    <row r="410" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A410" s="3" t="s">
         <v>788</v>
       </c>
@@ -44639,7 +44641,7 @@
       </c>
       <c r="T410" s="6"/>
     </row>
-    <row r="411" spans="1:20" ht="18">
+    <row r="411" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A411" s="7" t="s">
         <v>790</v>
       </c>
@@ -44697,7 +44699,7 @@
       </c>
       <c r="T411" s="6"/>
     </row>
-    <row r="412" spans="1:20" ht="18">
+    <row r="412" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A412" s="3" t="s">
         <v>791</v>
       </c>
@@ -44755,7 +44757,7 @@
       </c>
       <c r="T412" s="6"/>
     </row>
-    <row r="413" spans="1:20" ht="18">
+    <row r="413" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A413" s="7" t="s">
         <v>792</v>
       </c>
@@ -44813,7 +44815,7 @@
       </c>
       <c r="T413" s="6"/>
     </row>
-    <row r="414" spans="1:20" ht="18">
+    <row r="414" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A414" s="3" t="s">
         <v>793</v>
       </c>
@@ -44871,7 +44873,7 @@
       </c>
       <c r="T414" s="6"/>
     </row>
-    <row r="415" spans="1:20" ht="18">
+    <row r="415" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A415" s="7" t="s">
         <v>795</v>
       </c>
@@ -44929,7 +44931,7 @@
       </c>
       <c r="T415" s="6"/>
     </row>
-    <row r="416" spans="1:20" ht="18">
+    <row r="416" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A416" s="3" t="s">
         <v>796</v>
       </c>
@@ -44987,7 +44989,7 @@
       </c>
       <c r="T416" s="6"/>
     </row>
-    <row r="417" spans="1:20" ht="18">
+    <row r="417" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A417" s="7" t="s">
         <v>798</v>
       </c>
@@ -45045,7 +45047,7 @@
       </c>
       <c r="T417" s="6"/>
     </row>
-    <row r="418" spans="1:20" ht="18">
+    <row r="418" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A418" s="3" t="s">
         <v>799</v>
       </c>
@@ -45103,7 +45105,7 @@
       </c>
       <c r="T418" s="6"/>
     </row>
-    <row r="419" spans="1:20" ht="18">
+    <row r="419" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A419" s="7" t="s">
         <v>800</v>
       </c>
@@ -45161,7 +45163,7 @@
       </c>
       <c r="T419" s="6"/>
     </row>
-    <row r="420" spans="1:20" ht="18">
+    <row r="420" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A420" s="3" t="s">
         <v>802</v>
       </c>
@@ -45219,7 +45221,7 @@
       </c>
       <c r="T420" s="6"/>
     </row>
-    <row r="421" spans="1:20" ht="18">
+    <row r="421" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A421" s="7" t="s">
         <v>803</v>
       </c>
@@ -45277,7 +45279,7 @@
       </c>
       <c r="T421" s="6"/>
     </row>
-    <row r="422" spans="1:20" ht="18">
+    <row r="422" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A422" s="3" t="s">
         <v>805</v>
       </c>
@@ -45335,7 +45337,7 @@
       </c>
       <c r="T422" s="6"/>
     </row>
-    <row r="423" spans="1:20" ht="18">
+    <row r="423" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A423" s="7" t="s">
         <v>806</v>
       </c>
@@ -45393,7 +45395,7 @@
       </c>
       <c r="T423" s="6"/>
     </row>
-    <row r="424" spans="1:20" ht="18">
+    <row r="424" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A424" s="3" t="s">
         <v>807</v>
       </c>
@@ -45451,7 +45453,7 @@
       </c>
       <c r="T424" s="6"/>
     </row>
-    <row r="425" spans="1:20" ht="18">
+    <row r="425" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A425" s="7" t="s">
         <v>809</v>
       </c>
@@ -45509,7 +45511,7 @@
       </c>
       <c r="T425" s="6"/>
     </row>
-    <row r="426" spans="1:20" ht="18">
+    <row r="426" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A426" s="3" t="s">
         <v>810</v>
       </c>
@@ -45567,7 +45569,7 @@
       </c>
       <c r="T426" s="6"/>
     </row>
-    <row r="427" spans="1:20" ht="18">
+    <row r="427" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A427" s="7" t="s">
         <v>811</v>
       </c>
@@ -45625,7 +45627,7 @@
       </c>
       <c r="T427" s="6"/>
     </row>
-    <row r="428" spans="1:20" ht="18">
+    <row r="428" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A428" s="3" t="s">
         <v>813</v>
       </c>
@@ -45683,7 +45685,7 @@
       </c>
       <c r="T428" s="6"/>
     </row>
-    <row r="429" spans="1:20" ht="18">
+    <row r="429" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A429" s="7" t="s">
         <v>814</v>
       </c>
@@ -45741,7 +45743,7 @@
       </c>
       <c r="T429" s="6"/>
     </row>
-    <row r="430" spans="1:20" ht="18">
+    <row r="430" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A430" s="3" t="s">
         <v>815</v>
       </c>
@@ -45799,7 +45801,7 @@
       </c>
       <c r="T430" s="6"/>
     </row>
-    <row r="431" spans="1:20" ht="18">
+    <row r="431" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A431" s="7" t="s">
         <v>816</v>
       </c>
@@ -45857,7 +45859,7 @@
       </c>
       <c r="T431" s="6"/>
     </row>
-    <row r="432" spans="1:20" ht="18">
+    <row r="432" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A432" s="3" t="s">
         <v>818</v>
       </c>
@@ -45915,7 +45917,7 @@
       </c>
       <c r="T432" s="6"/>
     </row>
-    <row r="433" spans="1:20" ht="18">
+    <row r="433" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A433" s="7" t="s">
         <v>819</v>
       </c>
@@ -45973,7 +45975,7 @@
       </c>
       <c r="T433" s="6"/>
     </row>
-    <row r="434" spans="1:20" ht="18">
+    <row r="434" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A434" s="3" t="s">
         <v>821</v>
       </c>
@@ -46031,7 +46033,7 @@
       </c>
       <c r="T434" s="6"/>
     </row>
-    <row r="435" spans="1:20" ht="18">
+    <row r="435" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A435" s="7" t="s">
         <v>822</v>
       </c>
@@ -46089,7 +46091,7 @@
       </c>
       <c r="T435" s="6"/>
     </row>
-    <row r="436" spans="1:20" ht="18">
+    <row r="436" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A436" s="3" t="s">
         <v>823</v>
       </c>
@@ -46147,7 +46149,7 @@
       </c>
       <c r="T436" s="6"/>
     </row>
-    <row r="437" spans="1:20" ht="18">
+    <row r="437" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A437" s="7" t="s">
         <v>825</v>
       </c>
@@ -46205,7 +46207,7 @@
       </c>
       <c r="T437" s="6"/>
     </row>
-    <row r="438" spans="1:20" ht="18">
+    <row r="438" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A438" s="3" t="s">
         <v>826</v>
       </c>
@@ -46263,7 +46265,7 @@
       </c>
       <c r="T438" s="6"/>
     </row>
-    <row r="439" spans="1:20" ht="18">
+    <row r="439" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A439" s="7" t="s">
         <v>828</v>
       </c>
@@ -46321,7 +46323,7 @@
       </c>
       <c r="T439" s="6"/>
     </row>
-    <row r="440" spans="1:20" ht="18">
+    <row r="440" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A440" s="3" t="s">
         <v>830</v>
       </c>
@@ -46379,7 +46381,7 @@
       </c>
       <c r="T440" s="6"/>
     </row>
-    <row r="441" spans="1:20" ht="18">
+    <row r="441" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A441" s="7" t="s">
         <v>832</v>
       </c>
@@ -46437,7 +46439,7 @@
       </c>
       <c r="T441" s="6"/>
     </row>
-    <row r="442" spans="1:20" ht="18">
+    <row r="442" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A442" s="3" t="s">
         <v>833</v>
       </c>
@@ -46495,7 +46497,7 @@
       </c>
       <c r="T442" s="6"/>
     </row>
-    <row r="443" spans="1:20" ht="18">
+    <row r="443" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A443" s="7" t="s">
         <v>834</v>
       </c>
@@ -46553,7 +46555,7 @@
       </c>
       <c r="T443" s="6"/>
     </row>
-    <row r="444" spans="1:20" ht="18">
+    <row r="444" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A444" s="3" t="s">
         <v>836</v>
       </c>
@@ -46611,7 +46613,7 @@
       </c>
       <c r="T444" s="6"/>
     </row>
-    <row r="445" spans="1:20" ht="18">
+    <row r="445" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A445" s="7" t="s">
         <v>837</v>
       </c>
@@ -46669,7 +46671,7 @@
       </c>
       <c r="T445" s="6"/>
     </row>
-    <row r="446" spans="1:20" ht="18">
+    <row r="446" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A446" s="3" t="s">
         <v>838</v>
       </c>
@@ -46727,7 +46729,7 @@
       </c>
       <c r="T446" s="6"/>
     </row>
-    <row r="447" spans="1:20" ht="18">
+    <row r="447" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A447" s="7" t="s">
         <v>840</v>
       </c>
@@ -46785,7 +46787,7 @@
       </c>
       <c r="T447" s="6"/>
     </row>
-    <row r="448" spans="1:20" ht="18">
+    <row r="448" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A448" s="3" t="s">
         <v>842</v>
       </c>
@@ -46843,7 +46845,7 @@
       </c>
       <c r="T448" s="6"/>
     </row>
-    <row r="449" spans="1:20" ht="18">
+    <row r="449" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A449" s="7" t="s">
         <v>843</v>
       </c>
@@ -46901,7 +46903,7 @@
       </c>
       <c r="T449" s="6"/>
     </row>
-    <row r="450" spans="1:20" ht="18">
+    <row r="450" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A450" s="3" t="s">
         <v>845</v>
       </c>
@@ -46959,7 +46961,7 @@
       </c>
       <c r="T450" s="6"/>
     </row>
-    <row r="451" spans="1:20" ht="18">
+    <row r="451" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A451" s="7" t="s">
         <v>846</v>
       </c>
@@ -47017,7 +47019,7 @@
       </c>
       <c r="T451" s="6"/>
     </row>
-    <row r="452" spans="1:20" ht="18">
+    <row r="452" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A452" s="3" t="s">
         <v>848</v>
       </c>
@@ -47075,7 +47077,7 @@
       </c>
       <c r="T452" s="6"/>
     </row>
-    <row r="453" spans="1:20" ht="18">
+    <row r="453" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A453" s="7" t="s">
         <v>849</v>
       </c>
@@ -47133,7 +47135,7 @@
       </c>
       <c r="T453" s="6"/>
     </row>
-    <row r="454" spans="1:20" ht="18">
+    <row r="454" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A454" s="3" t="s">
         <v>850</v>
       </c>
@@ -47191,7 +47193,7 @@
       </c>
       <c r="T454" s="6"/>
     </row>
-    <row r="455" spans="1:20" ht="18">
+    <row r="455" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A455" s="7" t="s">
         <v>851</v>
       </c>
@@ -47249,7 +47251,7 @@
       </c>
       <c r="T455" s="6"/>
     </row>
-    <row r="456" spans="1:20" ht="18">
+    <row r="456" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A456" s="3" t="s">
         <v>853</v>
       </c>
@@ -47307,7 +47309,7 @@
       </c>
       <c r="T456" s="6"/>
     </row>
-    <row r="457" spans="1:20" ht="18">
+    <row r="457" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A457" s="7" t="s">
         <v>855</v>
       </c>
@@ -47365,7 +47367,7 @@
       </c>
       <c r="T457" s="6"/>
     </row>
-    <row r="458" spans="1:20" ht="18">
+    <row r="458" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A458" s="3" t="s">
         <v>856</v>
       </c>
@@ -47423,7 +47425,7 @@
       </c>
       <c r="T458" s="6"/>
     </row>
-    <row r="459" spans="1:20" ht="18">
+    <row r="459" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A459" s="7" t="s">
         <v>857</v>
       </c>
@@ -47481,7 +47483,7 @@
       </c>
       <c r="T459" s="6"/>
     </row>
-    <row r="460" spans="1:20" ht="18">
+    <row r="460" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A460" s="3" t="s">
         <v>858</v>
       </c>
@@ -47539,7 +47541,7 @@
       </c>
       <c r="T460" s="6"/>
     </row>
-    <row r="461" spans="1:20" ht="18">
+    <row r="461" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A461" s="7" t="s">
         <v>859</v>
       </c>
@@ -47597,7 +47599,7 @@
       </c>
       <c r="T461" s="6"/>
     </row>
-    <row r="462" spans="1:20" ht="18">
+    <row r="462" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A462" s="3" t="s">
         <v>860</v>
       </c>
@@ -47655,7 +47657,7 @@
       </c>
       <c r="T462" s="6"/>
     </row>
-    <row r="463" spans="1:20" ht="18">
+    <row r="463" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A463" s="7" t="s">
         <v>862</v>
       </c>
@@ -47713,7 +47715,7 @@
       </c>
       <c r="T463" s="6"/>
     </row>
-    <row r="464" spans="1:20" ht="18">
+    <row r="464" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A464" s="3" t="s">
         <v>864</v>
       </c>
@@ -47771,7 +47773,7 @@
       </c>
       <c r="T464" s="6"/>
     </row>
-    <row r="465" spans="1:20" ht="18">
+    <row r="465" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A465" s="7" t="s">
         <v>865</v>
       </c>
@@ -47829,7 +47831,7 @@
       </c>
       <c r="T465" s="6"/>
     </row>
-    <row r="466" spans="1:20" ht="18">
+    <row r="466" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A466" s="3" t="s">
         <v>866</v>
       </c>
@@ -47887,7 +47889,7 @@
       </c>
       <c r="T466" s="6"/>
     </row>
-    <row r="467" spans="1:20" ht="18">
+    <row r="467" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A467" s="7" t="s">
         <v>869</v>
       </c>
@@ -47945,7 +47947,7 @@
       </c>
       <c r="T467" s="6"/>
     </row>
-    <row r="468" spans="1:20" ht="18">
+    <row r="468" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A468" s="3" t="s">
         <v>870</v>
       </c>
@@ -48003,7 +48005,7 @@
       </c>
       <c r="T468" s="6"/>
     </row>
-    <row r="469" spans="1:20" ht="18">
+    <row r="469" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A469" s="7" t="s">
         <v>871</v>
       </c>
@@ -48061,7 +48063,7 @@
       </c>
       <c r="T469" s="6"/>
     </row>
-    <row r="470" spans="1:20" ht="18">
+    <row r="470" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A470" s="3" t="s">
         <v>872</v>
       </c>
@@ -48119,7 +48121,7 @@
       </c>
       <c r="T470" s="6"/>
     </row>
-    <row r="471" spans="1:20" ht="18">
+    <row r="471" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A471" s="7" t="s">
         <v>873</v>
       </c>
@@ -48177,7 +48179,7 @@
       </c>
       <c r="T471" s="6"/>
     </row>
-    <row r="472" spans="1:20" ht="18">
+    <row r="472" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A472" s="3" t="s">
         <v>874</v>
       </c>
@@ -48235,7 +48237,7 @@
       </c>
       <c r="T472" s="6"/>
     </row>
-    <row r="473" spans="1:20" ht="18">
+    <row r="473" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A473" s="7" t="s">
         <v>877</v>
       </c>
@@ -48293,7 +48295,7 @@
       </c>
       <c r="T473" s="6"/>
     </row>
-    <row r="474" spans="1:20" ht="18">
+    <row r="474" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A474" s="3" t="s">
         <v>879</v>
       </c>
@@ -48351,7 +48353,7 @@
       </c>
       <c r="T474" s="6"/>
     </row>
-    <row r="475" spans="1:20" ht="18">
+    <row r="475" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A475" s="7" t="s">
         <v>880</v>
       </c>
@@ -48409,7 +48411,7 @@
       </c>
       <c r="T475" s="6"/>
     </row>
-    <row r="476" spans="1:20" ht="18">
+    <row r="476" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A476" s="3" t="s">
         <v>882</v>
       </c>
@@ -48467,7 +48469,7 @@
       </c>
       <c r="T476" s="6"/>
     </row>
-    <row r="477" spans="1:20" ht="18">
+    <row r="477" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A477" s="7" t="s">
         <v>884</v>
       </c>
@@ -48525,7 +48527,7 @@
       </c>
       <c r="T477" s="6"/>
     </row>
-    <row r="478" spans="1:20" ht="18">
+    <row r="478" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A478" s="3" t="s">
         <v>886</v>
       </c>
@@ -48583,7 +48585,7 @@
       </c>
       <c r="T478" s="6"/>
     </row>
-    <row r="479" spans="1:20" ht="18">
+    <row r="479" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A479" s="7" t="s">
         <v>887</v>
       </c>
@@ -48641,7 +48643,7 @@
       </c>
       <c r="T479" s="6"/>
     </row>
-    <row r="480" spans="1:20" ht="18">
+    <row r="480" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A480" s="3" t="s">
         <v>889</v>
       </c>
@@ -48699,7 +48701,7 @@
       </c>
       <c r="T480" s="6"/>
     </row>
-    <row r="481" spans="1:20" ht="18">
+    <row r="481" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A481" s="7" t="s">
         <v>890</v>
       </c>
@@ -48757,7 +48759,7 @@
       </c>
       <c r="T481" s="6"/>
     </row>
-    <row r="482" spans="1:20" ht="18">
+    <row r="482" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A482" s="3" t="s">
         <v>891</v>
       </c>
@@ -48815,7 +48817,7 @@
       </c>
       <c r="T482" s="6"/>
     </row>
-    <row r="483" spans="1:20" ht="18">
+    <row r="483" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A483" s="7" t="s">
         <v>893</v>
       </c>
@@ -48873,7 +48875,7 @@
       </c>
       <c r="T483" s="6"/>
     </row>
-    <row r="484" spans="1:20" ht="18">
+    <row r="484" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A484" s="3" t="s">
         <v>895</v>
       </c>
@@ -48931,7 +48933,7 @@
       </c>
       <c r="T484" s="6"/>
     </row>
-    <row r="485" spans="1:20" ht="18">
+    <row r="485" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A485" s="7" t="s">
         <v>896</v>
       </c>
@@ -48989,7 +48991,7 @@
       </c>
       <c r="T485" s="6"/>
     </row>
-    <row r="486" spans="1:20" ht="18">
+    <row r="486" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A486" s="3" t="s">
         <v>897</v>
       </c>
@@ -49047,7 +49049,7 @@
       </c>
       <c r="T486" s="6"/>
     </row>
-    <row r="487" spans="1:20" ht="18">
+    <row r="487" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A487" s="7" t="s">
         <v>899</v>
       </c>
@@ -49105,7 +49107,7 @@
       </c>
       <c r="T487" s="6"/>
     </row>
-    <row r="488" spans="1:20" ht="18">
+    <row r="488" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A488" s="3" t="s">
         <v>901</v>
       </c>
@@ -49163,7 +49165,7 @@
       </c>
       <c r="T488" s="6"/>
     </row>
-    <row r="489" spans="1:20" ht="18">
+    <row r="489" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A489" s="7" t="s">
         <v>902</v>
       </c>
@@ -49221,7 +49223,7 @@
       </c>
       <c r="T489" s="6"/>
     </row>
-    <row r="490" spans="1:20" ht="18">
+    <row r="490" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A490" s="3" t="s">
         <v>905</v>
       </c>
@@ -49279,7 +49281,7 @@
       </c>
       <c r="T490" s="6"/>
     </row>
-    <row r="491" spans="1:20" ht="18">
+    <row r="491" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A491" s="7" t="s">
         <v>906</v>
       </c>
@@ -49337,7 +49339,7 @@
       </c>
       <c r="T491" s="6"/>
     </row>
-    <row r="492" spans="1:20" ht="18">
+    <row r="492" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A492" s="3" t="s">
         <v>907</v>
       </c>
@@ -49395,7 +49397,7 @@
       </c>
       <c r="T492" s="6"/>
     </row>
-    <row r="493" spans="1:20" ht="18">
+    <row r="493" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A493" s="7" t="s">
         <v>908</v>
       </c>
@@ -49453,7 +49455,7 @@
       </c>
       <c r="T493" s="6"/>
     </row>
-    <row r="494" spans="1:20" ht="18">
+    <row r="494" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A494" s="3" t="s">
         <v>909</v>
       </c>
@@ -49511,7 +49513,7 @@
       </c>
       <c r="T494" s="6"/>
     </row>
-    <row r="495" spans="1:20" ht="18">
+    <row r="495" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A495" s="7" t="s">
         <v>910</v>
       </c>
@@ -49569,7 +49571,7 @@
       </c>
       <c r="T495" s="6"/>
     </row>
-    <row r="496" spans="1:20" ht="18">
+    <row r="496" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A496" s="3" t="s">
         <v>911</v>
       </c>
@@ -49627,7 +49629,7 @@
       </c>
       <c r="T496" s="6"/>
     </row>
-    <row r="497" spans="1:20" ht="18">
+    <row r="497" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A497" s="7" t="s">
         <v>913</v>
       </c>
@@ -49685,7 +49687,7 @@
       </c>
       <c r="T497" s="6"/>
     </row>
-    <row r="498" spans="1:20" ht="18">
+    <row r="498" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A498" s="3" t="s">
         <v>914</v>
       </c>
@@ -49743,7 +49745,7 @@
       </c>
       <c r="T498" s="6"/>
     </row>
-    <row r="499" spans="1:20" ht="18">
+    <row r="499" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A499" s="7" t="s">
         <v>916</v>
       </c>
@@ -49801,7 +49803,7 @@
       </c>
       <c r="T499" s="6"/>
     </row>
-    <row r="500" spans="1:20" ht="18">
+    <row r="500" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A500" s="3" t="s">
         <v>918</v>
       </c>
@@ -49859,7 +49861,7 @@
       </c>
       <c r="T500" s="6"/>
     </row>
-    <row r="501" spans="1:20" ht="18">
+    <row r="501" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A501" s="7" t="s">
         <v>919</v>
       </c>
@@ -49917,7 +49919,7 @@
       </c>
       <c r="T501" s="6"/>
     </row>
-    <row r="502" spans="1:20" ht="18">
+    <row r="502" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A502" s="3" t="s">
         <v>921</v>
       </c>
@@ -49975,7 +49977,7 @@
       </c>
       <c r="T502" s="6"/>
     </row>
-    <row r="503" spans="1:20" ht="18">
+    <row r="503" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A503" s="7" t="s">
         <v>922</v>
       </c>
@@ -50033,7 +50035,7 @@
       </c>
       <c r="T503" s="6"/>
     </row>
-    <row r="504" spans="1:20" ht="18">
+    <row r="504" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A504" s="3" t="s">
         <v>923</v>
       </c>
@@ -50091,7 +50093,7 @@
       </c>
       <c r="T504" s="6"/>
     </row>
-    <row r="505" spans="1:20" ht="18">
+    <row r="505" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A505" s="7" t="s">
         <v>924</v>
       </c>
@@ -50149,7 +50151,7 @@
       </c>
       <c r="T505" s="6"/>
     </row>
-    <row r="506" spans="1:20" ht="18">
+    <row r="506" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A506" s="3" t="s">
         <v>926</v>
       </c>
@@ -50207,7 +50209,7 @@
       </c>
       <c r="T506" s="6"/>
     </row>
-    <row r="507" spans="1:20" ht="18">
+    <row r="507" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A507" s="7" t="s">
         <v>928</v>
       </c>
@@ -50261,7 +50263,7 @@
       </c>
       <c r="T507" s="6"/>
     </row>
-    <row r="508" spans="1:20" ht="18">
+    <row r="508" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A508" s="3" t="s">
         <v>930</v>
       </c>
@@ -50319,7 +50321,7 @@
       </c>
       <c r="T508" s="6"/>
     </row>
-    <row r="509" spans="1:20" ht="18">
+    <row r="509" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A509" s="7" t="s">
         <v>932</v>
       </c>
@@ -50377,7 +50379,7 @@
       </c>
       <c r="T509" s="6"/>
     </row>
-    <row r="510" spans="1:20" ht="18">
+    <row r="510" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A510" s="3" t="s">
         <v>933</v>
       </c>
@@ -50435,7 +50437,7 @@
       </c>
       <c r="T510" s="6"/>
     </row>
-    <row r="511" spans="1:20" ht="18">
+    <row r="511" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A511" s="7" t="s">
         <v>935</v>
       </c>
@@ -50493,7 +50495,7 @@
       </c>
       <c r="T511" s="6"/>
     </row>
-    <row r="512" spans="1:20" ht="18">
+    <row r="512" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A512" s="3" t="s">
         <v>936</v>
       </c>
@@ -50551,7 +50553,7 @@
       </c>
       <c r="T512" s="6"/>
     </row>
-    <row r="513" spans="1:20" ht="18">
+    <row r="513" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A513" s="7" t="s">
         <v>937</v>
       </c>
@@ -50609,7 +50611,7 @@
       </c>
       <c r="T513" s="6"/>
     </row>
-    <row r="514" spans="1:20" ht="18">
+    <row r="514" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A514" s="3" t="s">
         <v>938</v>
       </c>
@@ -50667,7 +50669,7 @@
       </c>
       <c r="T514" s="6"/>
     </row>
-    <row r="515" spans="1:20" ht="18">
+    <row r="515" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A515" s="7" t="s">
         <v>940</v>
       </c>
@@ -50725,7 +50727,7 @@
       </c>
       <c r="T515" s="6"/>
     </row>
-    <row r="516" spans="1:20" ht="18">
+    <row r="516" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A516" s="3" t="s">
         <v>941</v>
       </c>
@@ -50783,7 +50785,7 @@
       </c>
       <c r="T516" s="6"/>
     </row>
-    <row r="517" spans="1:20" ht="18">
+    <row r="517" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A517" s="7" t="s">
         <v>942</v>
       </c>
@@ -50841,7 +50843,7 @@
       </c>
       <c r="T517" s="6"/>
     </row>
-    <row r="518" spans="1:20" ht="18">
+    <row r="518" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A518" s="3" t="s">
         <v>944</v>
       </c>
@@ -50899,7 +50901,7 @@
       </c>
       <c r="T518" s="6"/>
     </row>
-    <row r="519" spans="1:20" ht="18">
+    <row r="519" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A519" s="7" t="s">
         <v>946</v>
       </c>
@@ -50957,7 +50959,7 @@
       </c>
       <c r="T519" s="6"/>
     </row>
-    <row r="520" spans="1:20" ht="18">
+    <row r="520" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A520" s="3" t="s">
         <v>948</v>
       </c>
@@ -51015,7 +51017,7 @@
       </c>
       <c r="T520" s="6"/>
     </row>
-    <row r="521" spans="1:20" ht="18">
+    <row r="521" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A521" s="7" t="s">
         <v>950</v>
       </c>
@@ -51073,7 +51075,7 @@
       </c>
       <c r="T521" s="6"/>
     </row>
-    <row r="522" spans="1:20" ht="18">
+    <row r="522" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A522" s="3" t="s">
         <v>951</v>
       </c>
@@ -51131,7 +51133,7 @@
       </c>
       <c r="T522" s="6"/>
     </row>
-    <row r="523" spans="1:20" ht="18">
+    <row r="523" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A523" s="7" t="s">
         <v>952</v>
       </c>
@@ -51189,7 +51191,7 @@
       </c>
       <c r="T523" s="6"/>
     </row>
-    <row r="524" spans="1:20" ht="18">
+    <row r="524" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A524" s="3" t="s">
         <v>953</v>
       </c>
@@ -51247,7 +51249,7 @@
       </c>
       <c r="T524" s="6"/>
     </row>
-    <row r="525" spans="1:20" ht="18">
+    <row r="525" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A525" s="7" t="s">
         <v>954</v>
       </c>
@@ -51305,7 +51307,7 @@
       </c>
       <c r="T525" s="6"/>
     </row>
-    <row r="526" spans="1:20" ht="18">
+    <row r="526" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A526" s="3" t="s">
         <v>955</v>
       </c>
@@ -51363,7 +51365,7 @@
       </c>
       <c r="T526" s="6"/>
     </row>
-    <row r="527" spans="1:20" ht="18">
+    <row r="527" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A527" s="7" t="s">
         <v>956</v>
       </c>
@@ -51421,7 +51423,7 @@
       </c>
       <c r="T527" s="6"/>
     </row>
-    <row r="528" spans="1:20" ht="18">
+    <row r="528" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A528" s="3" t="s">
         <v>958</v>
       </c>
@@ -51479,7 +51481,7 @@
       </c>
       <c r="T528" s="6"/>
     </row>
-    <row r="529" spans="1:20" ht="18">
+    <row r="529" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A529" s="7" t="s">
         <v>959</v>
       </c>
@@ -51537,7 +51539,7 @@
       </c>
       <c r="T529" s="6"/>
     </row>
-    <row r="530" spans="1:20" ht="18">
+    <row r="530" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A530" s="3" t="s">
         <v>961</v>
       </c>
@@ -51595,7 +51597,7 @@
       </c>
       <c r="T530" s="6"/>
     </row>
-    <row r="531" spans="1:20" ht="18">
+    <row r="531" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A531" s="7" t="s">
         <v>962</v>
       </c>
@@ -51653,7 +51655,7 @@
       </c>
       <c r="T531" s="6"/>
     </row>
-    <row r="532" spans="1:20" ht="18">
+    <row r="532" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A532" s="3" t="s">
         <v>964</v>
       </c>
@@ -51711,7 +51713,7 @@
       </c>
       <c r="T532" s="6"/>
     </row>
-    <row r="533" spans="1:20" ht="18">
+    <row r="533" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A533" s="7" t="s">
         <v>966</v>
       </c>
@@ -51769,7 +51771,7 @@
       </c>
       <c r="T533" s="6"/>
     </row>
-    <row r="534" spans="1:20" ht="18">
+    <row r="534" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A534" s="3" t="s">
         <v>967</v>
       </c>
@@ -51827,7 +51829,7 @@
       </c>
       <c r="T534" s="6"/>
     </row>
-    <row r="535" spans="1:20" ht="18">
+    <row r="535" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A535" s="7" t="s">
         <v>968</v>
       </c>
@@ -51885,7 +51887,7 @@
       </c>
       <c r="T535" s="6"/>
     </row>
-    <row r="536" spans="1:20" ht="18">
+    <row r="536" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A536" s="3" t="s">
         <v>969</v>
       </c>
@@ -51943,7 +51945,7 @@
       </c>
       <c r="T536" s="6"/>
     </row>
-    <row r="537" spans="1:20" ht="18">
+    <row r="537" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A537" s="7" t="s">
         <v>970</v>
       </c>
@@ -52001,7 +52003,7 @@
       </c>
       <c r="T537" s="6"/>
     </row>
-    <row r="538" spans="1:20" ht="18">
+    <row r="538" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A538" s="3" t="s">
         <v>971</v>
       </c>
@@ -52059,7 +52061,7 @@
       </c>
       <c r="T538" s="6"/>
     </row>
-    <row r="539" spans="1:20" ht="18">
+    <row r="539" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A539" s="7" t="s">
         <v>972</v>
       </c>
@@ -52117,7 +52119,7 @@
       </c>
       <c r="T539" s="6"/>
     </row>
-    <row r="540" spans="1:20" ht="18">
+    <row r="540" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A540" s="3" t="s">
         <v>973</v>
       </c>
@@ -52175,7 +52177,7 @@
       </c>
       <c r="T540" s="6"/>
     </row>
-    <row r="541" spans="1:20" ht="18">
+    <row r="541" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A541" s="7" t="s">
         <v>974</v>
       </c>
@@ -52233,7 +52235,7 @@
       </c>
       <c r="T541" s="6"/>
     </row>
-    <row r="542" spans="1:20" ht="18">
+    <row r="542" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A542" s="3" t="s">
         <v>975</v>
       </c>
@@ -52291,7 +52293,7 @@
       </c>
       <c r="T542" s="6"/>
     </row>
-    <row r="543" spans="1:20" ht="18">
+    <row r="543" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A543" s="7" t="s">
         <v>976</v>
       </c>
@@ -52349,7 +52351,7 @@
       </c>
       <c r="T543" s="6"/>
     </row>
-    <row r="544" spans="1:20" ht="18">
+    <row r="544" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A544" s="3" t="s">
         <v>977</v>
       </c>
@@ -52407,7 +52409,7 @@
       </c>
       <c r="T544" s="6"/>
     </row>
-    <row r="545" spans="1:20" ht="18">
+    <row r="545" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A545" s="7" t="s">
         <v>978</v>
       </c>
@@ -52465,7 +52467,7 @@
       </c>
       <c r="T545" s="6"/>
     </row>
-    <row r="546" spans="1:20" ht="18">
+    <row r="546" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A546" s="3" t="s">
         <v>979</v>
       </c>
@@ -52523,7 +52525,7 @@
       </c>
       <c r="T546" s="6"/>
     </row>
-    <row r="547" spans="1:20" ht="18">
+    <row r="547" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A547" s="7" t="s">
         <v>981</v>
       </c>
@@ -52581,7 +52583,7 @@
       </c>
       <c r="T547" s="6"/>
     </row>
-    <row r="548" spans="1:20" ht="18">
+    <row r="548" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A548" s="3" t="s">
         <v>983</v>
       </c>
@@ -52639,7 +52641,7 @@
       </c>
       <c r="T548" s="6"/>
     </row>
-    <row r="549" spans="1:20" ht="18">
+    <row r="549" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A549" s="7" t="s">
         <v>985</v>
       </c>
@@ -52697,7 +52699,7 @@
       </c>
       <c r="T549" s="6"/>
     </row>
-    <row r="550" spans="1:20" ht="18">
+    <row r="550" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A550" s="3" t="s">
         <v>986</v>
       </c>
@@ -52755,7 +52757,7 @@
       </c>
       <c r="T550" s="6"/>
     </row>
-    <row r="551" spans="1:20" ht="18">
+    <row r="551" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A551" s="7" t="s">
         <v>987</v>
       </c>
@@ -52813,7 +52815,7 @@
       </c>
       <c r="T551" s="6"/>
     </row>
-    <row r="552" spans="1:20" ht="18">
+    <row r="552" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A552" s="3" t="s">
         <v>989</v>
       </c>
@@ -52871,7 +52873,7 @@
       </c>
       <c r="T552" s="6"/>
     </row>
-    <row r="553" spans="1:20" ht="18">
+    <row r="553" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A553" s="7" t="s">
         <v>991</v>
       </c>
@@ -52929,7 +52931,7 @@
       </c>
       <c r="T553" s="6"/>
     </row>
-    <row r="554" spans="1:20" ht="18">
+    <row r="554" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A554" s="3" t="s">
         <v>992</v>
       </c>
@@ -52987,7 +52989,7 @@
       </c>
       <c r="T554" s="6"/>
     </row>
-    <row r="555" spans="1:20" ht="18">
+    <row r="555" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A555" s="7" t="s">
         <v>994</v>
       </c>
@@ -53045,7 +53047,7 @@
       </c>
       <c r="T555" s="6"/>
     </row>
-    <row r="556" spans="1:20" ht="18">
+    <row r="556" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A556" s="3" t="s">
         <v>995</v>
       </c>
@@ -53101,7 +53103,7 @@
       </c>
       <c r="T556" s="6"/>
     </row>
-    <row r="557" spans="1:20" ht="18">
+    <row r="557" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A557" s="7" t="s">
         <v>996</v>
       </c>
@@ -53159,7 +53161,7 @@
       </c>
       <c r="T557" s="6"/>
     </row>
-    <row r="558" spans="1:20" ht="18">
+    <row r="558" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A558" s="3" t="s">
         <v>998</v>
       </c>
@@ -53217,7 +53219,7 @@
       </c>
       <c r="T558" s="6"/>
     </row>
-    <row r="559" spans="1:20" ht="18">
+    <row r="559" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A559" s="7" t="s">
         <v>1000</v>
       </c>
@@ -53275,7 +53277,7 @@
       </c>
       <c r="T559" s="6"/>
     </row>
-    <row r="560" spans="1:20" ht="18">
+    <row r="560" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A560" s="3" t="s">
         <v>1002</v>
       </c>
@@ -53333,7 +53335,7 @@
       </c>
       <c r="T560" s="6"/>
     </row>
-    <row r="561" spans="1:20" ht="18">
+    <row r="561" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A561" s="7" t="s">
         <v>1003</v>
       </c>
@@ -53391,7 +53393,7 @@
       </c>
       <c r="T561" s="6"/>
     </row>
-    <row r="562" spans="1:20" ht="18">
+    <row r="562" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A562" s="3" t="s">
         <v>1004</v>
       </c>
@@ -53449,7 +53451,7 @@
       </c>
       <c r="T562" s="6"/>
     </row>
-    <row r="563" spans="1:20" ht="18">
+    <row r="563" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A563" s="7" t="s">
         <v>1006</v>
       </c>
@@ -53507,7 +53509,7 @@
       </c>
       <c r="T563" s="6"/>
     </row>
-    <row r="564" spans="1:20" ht="18">
+    <row r="564" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A564" s="3" t="s">
         <v>1007</v>
       </c>
@@ -53565,7 +53567,7 @@
       </c>
       <c r="T564" s="6"/>
     </row>
-    <row r="565" spans="1:20" ht="18">
+    <row r="565" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A565" s="7" t="s">
         <v>1009</v>
       </c>
@@ -53623,7 +53625,7 @@
       </c>
       <c r="T565" s="6"/>
     </row>
-    <row r="566" spans="1:20" ht="18">
+    <row r="566" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A566" s="3" t="s">
         <v>1010</v>
       </c>
@@ -53681,7 +53683,7 @@
       </c>
       <c r="T566" s="6"/>
     </row>
-    <row r="567" spans="1:20" ht="18">
+    <row r="567" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A567" s="7" t="s">
         <v>1012</v>
       </c>
@@ -53739,7 +53741,7 @@
       </c>
       <c r="T567" s="6"/>
     </row>
-    <row r="568" spans="1:20" ht="18">
+    <row r="568" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A568" s="3" t="s">
         <v>1014</v>
       </c>
@@ -53797,7 +53799,7 @@
       </c>
       <c r="T568" s="6"/>
     </row>
-    <row r="569" spans="1:20" ht="18">
+    <row r="569" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A569" s="7" t="s">
         <v>1015</v>
       </c>
@@ -53855,7 +53857,7 @@
       </c>
       <c r="T569" s="6"/>
     </row>
-    <row r="570" spans="1:20" ht="18">
+    <row r="570" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A570" s="3" t="s">
         <v>1017</v>
       </c>
@@ -53913,7 +53915,7 @@
       </c>
       <c r="T570" s="6"/>
     </row>
-    <row r="571" spans="1:20" ht="18">
+    <row r="571" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A571" s="7" t="s">
         <v>1018</v>
       </c>
@@ -53971,7 +53973,7 @@
       </c>
       <c r="T571" s="6"/>
     </row>
-    <row r="572" spans="1:20" ht="18">
+    <row r="572" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A572" s="3" t="s">
         <v>1020</v>
       </c>
@@ -54029,7 +54031,7 @@
       </c>
       <c r="T572" s="6"/>
     </row>
-    <row r="573" spans="1:20" ht="18">
+    <row r="573" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A573" s="7" t="s">
         <v>1021</v>
       </c>
@@ -54087,7 +54089,7 @@
       </c>
       <c r="T573" s="6"/>
     </row>
-    <row r="574" spans="1:20" ht="18">
+    <row r="574" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A574" s="3" t="s">
         <v>1022</v>
       </c>
@@ -54145,7 +54147,7 @@
       </c>
       <c r="T574" s="6"/>
     </row>
-    <row r="575" spans="1:20" ht="18">
+    <row r="575" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A575" s="7" t="s">
         <v>1024</v>
       </c>
@@ -54203,7 +54205,7 @@
       </c>
       <c r="T575" s="6"/>
     </row>
-    <row r="576" spans="1:20" ht="18">
+    <row r="576" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A576" s="3" t="s">
         <v>1025</v>
       </c>
@@ -54261,7 +54263,7 @@
       </c>
       <c r="T576" s="6"/>
     </row>
-    <row r="577" spans="1:20" ht="18">
+    <row r="577" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A577" s="7" t="s">
         <v>1027</v>
       </c>
@@ -54319,7 +54321,7 @@
       </c>
       <c r="T577" s="6"/>
     </row>
-    <row r="578" spans="1:20" ht="18">
+    <row r="578" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A578" s="3" t="s">
         <v>1029</v>
       </c>
@@ -54377,7 +54379,7 @@
       </c>
       <c r="T578" s="6"/>
     </row>
-    <row r="579" spans="1:20" ht="18">
+    <row r="579" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A579" s="7" t="s">
         <v>1031</v>
       </c>
@@ -54435,7 +54437,7 @@
       </c>
       <c r="T579" s="6"/>
     </row>
-    <row r="580" spans="1:20" ht="18">
+    <row r="580" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A580" s="3" t="s">
         <v>1033</v>
       </c>
@@ -54493,7 +54495,7 @@
       </c>
       <c r="T580" s="6"/>
     </row>
-    <row r="581" spans="1:20" ht="18">
+    <row r="581" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A581" s="7" t="s">
         <v>1034</v>
       </c>
@@ -54551,7 +54553,7 @@
       </c>
       <c r="T581" s="6"/>
     </row>
-    <row r="582" spans="1:20" ht="18">
+    <row r="582" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A582" s="3" t="s">
         <v>1035</v>
       </c>
@@ -54609,7 +54611,7 @@
       </c>
       <c r="T582" s="6"/>
     </row>
-    <row r="583" spans="1:20" ht="18">
+    <row r="583" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A583" s="7" t="s">
         <v>1037</v>
       </c>
@@ -54667,7 +54669,7 @@
       </c>
       <c r="T583" s="6"/>
     </row>
-    <row r="584" spans="1:20" ht="18">
+    <row r="584" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A584" s="3" t="s">
         <v>1039</v>
       </c>
@@ -54725,7 +54727,7 @@
       </c>
       <c r="T584" s="6"/>
     </row>
-    <row r="585" spans="1:20" ht="18">
+    <row r="585" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A585" s="7" t="s">
         <v>1040</v>
       </c>
@@ -54783,7 +54785,7 @@
       </c>
       <c r="T585" s="6"/>
     </row>
-    <row r="586" spans="1:20" ht="18">
+    <row r="586" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A586" s="3" t="s">
         <v>1042</v>
       </c>
@@ -54841,7 +54843,7 @@
       </c>
       <c r="T586" s="6"/>
     </row>
-    <row r="587" spans="1:20" ht="18">
+    <row r="587" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A587" s="7" t="s">
         <v>1044</v>
       </c>
@@ -54899,7 +54901,7 @@
       </c>
       <c r="T587" s="6"/>
     </row>
-    <row r="588" spans="1:20" ht="18">
+    <row r="588" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A588" s="3" t="s">
         <v>1045</v>
       </c>
@@ -54957,7 +54959,7 @@
       </c>
       <c r="T588" s="6"/>
     </row>
-    <row r="589" spans="1:20" ht="18">
+    <row r="589" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A589" s="7" t="s">
         <v>1046</v>
       </c>
@@ -55015,7 +55017,7 @@
       </c>
       <c r="T589" s="6"/>
     </row>
-    <row r="590" spans="1:20" ht="18">
+    <row r="590" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A590" s="3" t="s">
         <v>1047</v>
       </c>
@@ -55073,7 +55075,7 @@
       </c>
       <c r="T590" s="6"/>
     </row>
-    <row r="591" spans="1:20" ht="18">
+    <row r="591" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A591" s="7" t="s">
         <v>1048</v>
       </c>
@@ -55131,7 +55133,7 @@
       </c>
       <c r="T591" s="6"/>
     </row>
-    <row r="592" spans="1:20" ht="18">
+    <row r="592" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A592" s="3" t="s">
         <v>1050</v>
       </c>
@@ -55189,7 +55191,7 @@
       </c>
       <c r="T592" s="6"/>
     </row>
-    <row r="593" spans="1:20" ht="18">
+    <row r="593" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A593" s="7" t="s">
         <v>1051</v>
       </c>
@@ -55247,7 +55249,7 @@
       </c>
       <c r="T593" s="6"/>
     </row>
-    <row r="594" spans="1:20" ht="18">
+    <row r="594" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A594" s="3" t="s">
         <v>1052</v>
       </c>
@@ -55305,7 +55307,7 @@
       </c>
       <c r="T594" s="6"/>
     </row>
-    <row r="595" spans="1:20" ht="18">
+    <row r="595" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A595" s="7" t="s">
         <v>1053</v>
       </c>
@@ -55363,7 +55365,7 @@
       </c>
       <c r="T595" s="6"/>
     </row>
-    <row r="596" spans="1:20" ht="18">
+    <row r="596" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A596" s="3" t="s">
         <v>1054</v>
       </c>
@@ -55421,7 +55423,7 @@
       </c>
       <c r="T596" s="6"/>
     </row>
-    <row r="597" spans="1:20" ht="18">
+    <row r="597" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A597" s="7" t="s">
         <v>1055</v>
       </c>
@@ -55479,7 +55481,7 @@
       </c>
       <c r="T597" s="6"/>
     </row>
-    <row r="598" spans="1:20" ht="18">
+    <row r="598" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A598" s="3" t="s">
         <v>1056</v>
       </c>
@@ -55537,7 +55539,7 @@
       </c>
       <c r="T598" s="6"/>
     </row>
-    <row r="599" spans="1:20" ht="18">
+    <row r="599" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A599" s="7" t="s">
         <v>1058</v>
       </c>
@@ -55595,7 +55597,7 @@
       </c>
       <c r="T599" s="6"/>
     </row>
-    <row r="600" spans="1:20" ht="18">
+    <row r="600" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A600" s="3" t="s">
         <v>1059</v>
       </c>
@@ -55653,7 +55655,7 @@
       </c>
       <c r="T600" s="6"/>
     </row>
-    <row r="601" spans="1:20" ht="18">
+    <row r="601" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A601" s="7" t="s">
         <v>1061</v>
       </c>
@@ -55711,7 +55713,7 @@
       </c>
       <c r="T601" s="6"/>
     </row>
-    <row r="602" spans="1:20" ht="18">
+    <row r="602" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A602" s="3" t="s">
         <v>1062</v>
       </c>
@@ -55769,7 +55771,7 @@
       </c>
       <c r="T602" s="6"/>
     </row>
-    <row r="603" spans="1:20" ht="18">
+    <row r="603" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A603" s="7" t="s">
         <v>1063</v>
       </c>
@@ -55827,7 +55829,7 @@
       </c>
       <c r="T603" s="6"/>
     </row>
-    <row r="604" spans="1:20" ht="18">
+    <row r="604" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A604" s="3" t="s">
         <v>1065</v>
       </c>
@@ -55881,7 +55883,7 @@
       </c>
       <c r="T604" s="6"/>
     </row>
-    <row r="605" spans="1:20" ht="18">
+    <row r="605" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A605" s="7" t="s">
         <v>1066</v>
       </c>
@@ -55939,7 +55941,7 @@
       </c>
       <c r="T605" s="6"/>
     </row>
-    <row r="606" spans="1:20" ht="18">
+    <row r="606" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A606" s="3" t="s">
         <v>1067</v>
       </c>
@@ -55997,7 +55999,7 @@
       </c>
       <c r="T606" s="6"/>
     </row>
-    <row r="607" spans="1:20" ht="18">
+    <row r="607" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A607" s="7" t="s">
         <v>1069</v>
       </c>
@@ -56055,7 +56057,7 @@
       </c>
       <c r="T607" s="6"/>
     </row>
-    <row r="608" spans="1:20" ht="18">
+    <row r="608" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A608" s="3" t="s">
         <v>1070</v>
       </c>
@@ -56113,7 +56115,7 @@
       </c>
       <c r="T608" s="6"/>
     </row>
-    <row r="609" spans="1:20" ht="18">
+    <row r="609" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A609" s="7" t="s">
         <v>1072</v>
       </c>
@@ -56171,7 +56173,7 @@
       </c>
       <c r="T609" s="6"/>
     </row>
-    <row r="610" spans="1:20" ht="18">
+    <row r="610" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A610" s="3" t="s">
         <v>1073</v>
       </c>
@@ -56229,7 +56231,7 @@
       </c>
       <c r="T610" s="6"/>
     </row>
-    <row r="611" spans="1:20" ht="18">
+    <row r="611" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A611" s="7" t="s">
         <v>1074</v>
       </c>
@@ -56287,7 +56289,7 @@
       </c>
       <c r="T611" s="6"/>
     </row>
-    <row r="612" spans="1:20" ht="18">
+    <row r="612" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A612" s="3" t="s">
         <v>1075</v>
       </c>
@@ -56345,7 +56347,7 @@
       </c>
       <c r="T612" s="6"/>
     </row>
-    <row r="613" spans="1:20" ht="18">
+    <row r="613" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A613" s="7" t="s">
         <v>1076</v>
       </c>
@@ -56403,7 +56405,7 @@
       </c>
       <c r="T613" s="6"/>
     </row>
-    <row r="614" spans="1:20" ht="18">
+    <row r="614" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A614" s="3" t="s">
         <v>1077</v>
       </c>
@@ -56461,7 +56463,7 @@
       </c>
       <c r="T614" s="6"/>
     </row>
-    <row r="615" spans="1:20" ht="18">
+    <row r="615" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A615" s="7" t="s">
         <v>1078</v>
       </c>
@@ -56519,7 +56521,7 @@
       </c>
       <c r="T615" s="6"/>
     </row>
-    <row r="616" spans="1:20" ht="18">
+    <row r="616" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A616" s="3" t="s">
         <v>1080</v>
       </c>
@@ -56577,7 +56579,7 @@
       </c>
       <c r="T616" s="6"/>
     </row>
-    <row r="617" spans="1:20" ht="18">
+    <row r="617" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A617" s="7" t="s">
         <v>1082</v>
       </c>
@@ -56635,7 +56637,7 @@
       </c>
       <c r="T617" s="6"/>
     </row>
-    <row r="618" spans="1:20" ht="18">
+    <row r="618" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A618" s="3" t="s">
         <v>1083</v>
       </c>
@@ -56693,7 +56695,7 @@
       </c>
       <c r="T618" s="6"/>
     </row>
-    <row r="619" spans="1:20" ht="18">
+    <row r="619" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A619" s="7" t="s">
         <v>1084</v>
       </c>
@@ -56751,7 +56753,7 @@
       </c>
       <c r="T619" s="6"/>
     </row>
-    <row r="620" spans="1:20" ht="18">
+    <row r="620" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A620" s="3" t="s">
         <v>1085</v>
       </c>
@@ -56809,7 +56811,7 @@
       </c>
       <c r="T620" s="6"/>
     </row>
-    <row r="621" spans="1:20" ht="18">
+    <row r="621" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A621" s="7" t="s">
         <v>1087</v>
       </c>
@@ -56867,7 +56869,7 @@
       </c>
       <c r="T621" s="6"/>
     </row>
-    <row r="622" spans="1:20" ht="18">
+    <row r="622" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A622" s="3" t="s">
         <v>1089</v>
       </c>
@@ -56925,7 +56927,7 @@
       </c>
       <c r="T622" s="6"/>
     </row>
-    <row r="623" spans="1:20" ht="18">
+    <row r="623" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A623" s="7" t="s">
         <v>1090</v>
       </c>
@@ -56983,7 +56985,7 @@
       </c>
       <c r="T623" s="6"/>
     </row>
-    <row r="624" spans="1:20" ht="18">
+    <row r="624" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A624" s="3" t="s">
         <v>1091</v>
       </c>
@@ -57041,7 +57043,7 @@
       </c>
       <c r="T624" s="6"/>
     </row>
-    <row r="625" spans="1:20" ht="18">
+    <row r="625" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A625" s="7" t="s">
         <v>1092</v>
       </c>
@@ -57099,7 +57101,7 @@
       </c>
       <c r="T625" s="6"/>
     </row>
-    <row r="626" spans="1:20" ht="18">
+    <row r="626" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A626" s="3" t="s">
         <v>1093</v>
       </c>
@@ -57157,7 +57159,7 @@
       </c>
       <c r="T626" s="6"/>
     </row>
-    <row r="627" spans="1:20" ht="18">
+    <row r="627" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A627" s="7" t="s">
         <v>1094</v>
       </c>
@@ -57215,7 +57217,7 @@
       </c>
       <c r="T627" s="6"/>
     </row>
-    <row r="628" spans="1:20" ht="18">
+    <row r="628" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A628" s="3" t="s">
         <v>1095</v>
       </c>
@@ -57273,7 +57275,7 @@
       </c>
       <c r="T628" s="6"/>
     </row>
-    <row r="629" spans="1:20" ht="18">
+    <row r="629" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A629" s="7" t="s">
         <v>1096</v>
       </c>
@@ -57331,7 +57333,7 @@
       </c>
       <c r="T629" s="6"/>
     </row>
-    <row r="630" spans="1:20" ht="18">
+    <row r="630" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A630" s="3" t="s">
         <v>1097</v>
       </c>
@@ -57389,7 +57391,7 @@
       </c>
       <c r="T630" s="6"/>
     </row>
-    <row r="631" spans="1:20" ht="18">
+    <row r="631" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A631" s="7" t="s">
         <v>1100</v>
       </c>
@@ -57447,7 +57449,7 @@
       </c>
       <c r="T631" s="6"/>
     </row>
-    <row r="632" spans="1:20" ht="18">
+    <row r="632" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A632" s="3" t="s">
         <v>1101</v>
       </c>
@@ -57505,7 +57507,7 @@
       </c>
       <c r="T632" s="6"/>
     </row>
-    <row r="633" spans="1:20" ht="18">
+    <row r="633" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A633" s="7" t="s">
         <v>1103</v>
       </c>
@@ -57563,7 +57565,7 @@
       </c>
       <c r="T633" s="6"/>
     </row>
-    <row r="634" spans="1:20" ht="18">
+    <row r="634" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A634" s="3" t="s">
         <v>1105</v>
       </c>
@@ -57621,7 +57623,7 @@
       </c>
       <c r="T634" s="6"/>
     </row>
-    <row r="635" spans="1:20" ht="18">
+    <row r="635" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A635" s="7" t="s">
         <v>1106</v>
       </c>
@@ -57679,7 +57681,7 @@
       </c>
       <c r="T635" s="6"/>
     </row>
-    <row r="636" spans="1:20" ht="18">
+    <row r="636" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A636" s="3" t="s">
         <v>1107</v>
       </c>
@@ -57737,7 +57739,7 @@
       </c>
       <c r="T636" s="6"/>
     </row>
-    <row r="637" spans="1:20" ht="18">
+    <row r="637" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A637" s="7" t="s">
         <v>1109</v>
       </c>
@@ -57795,7 +57797,7 @@
       </c>
       <c r="T637" s="6"/>
     </row>
-    <row r="638" spans="1:20" ht="18">
+    <row r="638" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A638" s="3" t="s">
         <v>1110</v>
       </c>
@@ -57853,7 +57855,7 @@
       </c>
       <c r="T638" s="6"/>
     </row>
-    <row r="639" spans="1:20" ht="18">
+    <row r="639" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A639" s="7" t="s">
         <v>1113</v>
       </c>
@@ -57911,7 +57913,7 @@
       </c>
       <c r="T639" s="6"/>
     </row>
-    <row r="640" spans="1:20" ht="18">
+    <row r="640" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A640" s="3" t="s">
         <v>1114</v>
       </c>
@@ -57969,7 +57971,7 @@
       </c>
       <c r="T640" s="6"/>
     </row>
-    <row r="641" spans="1:20" ht="18">
+    <row r="641" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A641" s="7" t="s">
         <v>1115</v>
       </c>
@@ -58027,7 +58029,7 @@
       </c>
       <c r="T641" s="6"/>
     </row>
-    <row r="642" spans="1:20" ht="18">
+    <row r="642" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A642" s="3" t="s">
         <v>1116</v>
       </c>
@@ -58085,7 +58087,7 @@
       </c>
       <c r="T642" s="6"/>
     </row>
-    <row r="643" spans="1:20" ht="18">
+    <row r="643" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A643" s="7" t="s">
         <v>1118</v>
       </c>
@@ -58143,7 +58145,7 @@
       </c>
       <c r="T643" s="6"/>
     </row>
-    <row r="644" spans="1:20" ht="18">
+    <row r="644" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A644" s="3" t="s">
         <v>1120</v>
       </c>
@@ -58201,7 +58203,7 @@
       </c>
       <c r="T644" s="6"/>
     </row>
-    <row r="645" spans="1:20" ht="18">
+    <row r="645" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A645" s="7" t="s">
         <v>1121</v>
       </c>
@@ -58259,7 +58261,7 @@
       </c>
       <c r="T645" s="6"/>
     </row>
-    <row r="646" spans="1:20" ht="18">
+    <row r="646" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A646" s="3" t="s">
         <v>1123</v>
       </c>
@@ -58317,7 +58319,7 @@
       </c>
       <c r="T646" s="6"/>
     </row>
-    <row r="647" spans="1:20" ht="18">
+    <row r="647" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A647" s="7" t="s">
         <v>1124</v>
       </c>
@@ -58375,7 +58377,7 @@
       </c>
       <c r="T647" s="6"/>
     </row>
-    <row r="648" spans="1:20" ht="18">
+    <row r="648" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A648" s="3" t="s">
         <v>1125</v>
       </c>
@@ -58433,7 +58435,7 @@
       </c>
       <c r="T648" s="6"/>
     </row>
-    <row r="649" spans="1:20" ht="18">
+    <row r="649" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A649" s="7" t="s">
         <v>1126</v>
       </c>
@@ -58491,7 +58493,7 @@
       </c>
       <c r="T649" s="6"/>
     </row>
-    <row r="650" spans="1:20" ht="18">
+    <row r="650" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A650" s="3" t="s">
         <v>1127</v>
       </c>
@@ -58549,7 +58551,7 @@
       </c>
       <c r="T650" s="6"/>
     </row>
-    <row r="651" spans="1:20" ht="18">
+    <row r="651" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A651" s="7" t="s">
         <v>1128</v>
       </c>
@@ -58607,7 +58609,7 @@
       </c>
       <c r="T651" s="6"/>
     </row>
-    <row r="652" spans="1:20" ht="18">
+    <row r="652" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A652" s="3" t="s">
         <v>1130</v>
       </c>
@@ -58665,7 +58667,7 @@
       </c>
       <c r="T652" s="6"/>
     </row>
-    <row r="653" spans="1:20" ht="18">
+    <row r="653" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A653" s="7" t="s">
         <v>1131</v>
       </c>
@@ -58723,7 +58725,7 @@
       </c>
       <c r="T653" s="6"/>
     </row>
-    <row r="654" spans="1:20" ht="18">
+    <row r="654" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A654" s="3" t="s">
         <v>1133</v>
       </c>
@@ -58781,7 +58783,7 @@
       </c>
       <c r="T654" s="6"/>
     </row>
-    <row r="655" spans="1:20" ht="18">
+    <row r="655" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A655" s="7" t="s">
         <v>1134</v>
       </c>
@@ -58835,7 +58837,7 @@
       </c>
       <c r="T655" s="6"/>
     </row>
-    <row r="656" spans="1:20" ht="18">
+    <row r="656" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A656" s="3" t="s">
         <v>1136</v>
       </c>
@@ -58893,7 +58895,7 @@
       </c>
       <c r="T656" s="6"/>
     </row>
-    <row r="657" spans="1:20" ht="18">
+    <row r="657" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A657" s="7" t="s">
         <v>1138</v>
       </c>
@@ -58951,7 +58953,7 @@
       </c>
       <c r="T657" s="6"/>
     </row>
-    <row r="658" spans="1:20" ht="18">
+    <row r="658" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A658" s="3" t="s">
         <v>1140</v>
       </c>
@@ -59009,7 +59011,7 @@
       </c>
       <c r="T658" s="6"/>
     </row>
-    <row r="659" spans="1:20" ht="18">
+    <row r="659" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A659" s="7" t="s">
         <v>1142</v>
       </c>
@@ -59067,7 +59069,7 @@
       </c>
       <c r="T659" s="6"/>
     </row>
-    <row r="660" spans="1:20" ht="18">
+    <row r="660" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A660" s="3" t="s">
         <v>1143</v>
       </c>
@@ -59125,7 +59127,7 @@
       </c>
       <c r="T660" s="6"/>
     </row>
-    <row r="661" spans="1:20" ht="18">
+    <row r="661" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A661" s="7" t="s">
         <v>1144</v>
       </c>
@@ -59183,7 +59185,7 @@
       </c>
       <c r="T661" s="6"/>
     </row>
-    <row r="662" spans="1:20" ht="18">
+    <row r="662" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A662" s="3" t="s">
         <v>1145</v>
       </c>
@@ -59241,7 +59243,7 @@
       </c>
       <c r="T662" s="6"/>
     </row>
-    <row r="663" spans="1:20" ht="18">
+    <row r="663" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A663" s="7" t="s">
         <v>1146</v>
       </c>
@@ -59299,7 +59301,7 @@
       </c>
       <c r="T663" s="6"/>
     </row>
-    <row r="664" spans="1:20" ht="18">
+    <row r="664" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A664" s="3" t="s">
         <v>1147</v>
       </c>
@@ -59357,7 +59359,7 @@
       </c>
       <c r="T664" s="6"/>
     </row>
-    <row r="665" spans="1:20" ht="18">
+    <row r="665" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A665" s="7" t="s">
         <v>1148</v>
       </c>
@@ -59415,7 +59417,7 @@
       </c>
       <c r="T665" s="6"/>
     </row>
-    <row r="666" spans="1:20" ht="18">
+    <row r="666" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A666" s="3" t="s">
         <v>1149</v>
       </c>
@@ -59473,7 +59475,7 @@
       </c>
       <c r="T666" s="6"/>
     </row>
-    <row r="667" spans="1:20" ht="18">
+    <row r="667" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A667" s="7" t="s">
         <v>1151</v>
       </c>
@@ -59531,7 +59533,7 @@
       </c>
       <c r="T667" s="6"/>
     </row>
-    <row r="668" spans="1:20" ht="18">
+    <row r="668" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A668" s="3" t="s">
         <v>1153</v>
       </c>
@@ -59589,7 +59591,7 @@
       </c>
       <c r="T668" s="6"/>
     </row>
-    <row r="669" spans="1:20" ht="18">
+    <row r="669" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A669" s="7" t="s">
         <v>1154</v>
       </c>
@@ -59647,7 +59649,7 @@
       </c>
       <c r="T669" s="6"/>
     </row>
-    <row r="670" spans="1:20" ht="18">
+    <row r="670" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A670" s="3" t="s">
         <v>1155</v>
       </c>
@@ -59705,7 +59707,7 @@
       </c>
       <c r="T670" s="6"/>
     </row>
-    <row r="671" spans="1:20" ht="18">
+    <row r="671" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A671" s="7" t="s">
         <v>1156</v>
       </c>
@@ -59763,7 +59765,7 @@
       </c>
       <c r="T671" s="6"/>
     </row>
-    <row r="672" spans="1:20" ht="18">
+    <row r="672" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A672" s="3" t="s">
         <v>1157</v>
       </c>
@@ -59821,7 +59823,7 @@
       </c>
       <c r="T672" s="6"/>
     </row>
-    <row r="673" spans="1:20" ht="18">
+    <row r="673" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A673" s="7" t="s">
         <v>1158</v>
       </c>
@@ -59879,7 +59881,7 @@
       </c>
       <c r="T673" s="6"/>
     </row>
-    <row r="674" spans="1:20" ht="18">
+    <row r="674" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A674" s="3" t="s">
         <v>1159</v>
       </c>
@@ -59937,7 +59939,7 @@
       </c>
       <c r="T674" s="6"/>
     </row>
-    <row r="675" spans="1:20" ht="18">
+    <row r="675" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A675" s="7" t="s">
         <v>1160</v>
       </c>
@@ -59995,7 +59997,7 @@
       </c>
       <c r="T675" s="6"/>
     </row>
-    <row r="676" spans="1:20" ht="18">
+    <row r="676" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A676" s="3" t="s">
         <v>1161</v>
       </c>
@@ -60053,7 +60055,7 @@
       </c>
       <c r="T676" s="6"/>
     </row>
-    <row r="677" spans="1:20" ht="18">
+    <row r="677" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A677" s="7" t="s">
         <v>1163</v>
       </c>
@@ -60111,7 +60113,7 @@
       </c>
       <c r="T677" s="6"/>
     </row>
-    <row r="678" spans="1:20" ht="18">
+    <row r="678" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A678" s="3" t="s">
         <v>1164</v>
       </c>
@@ -60169,7 +60171,7 @@
       </c>
       <c r="T678" s="6"/>
     </row>
-    <row r="679" spans="1:20" ht="18">
+    <row r="679" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A679" s="7" t="s">
         <v>1165</v>
       </c>
@@ -60227,7 +60229,7 @@
       </c>
       <c r="T679" s="6"/>
     </row>
-    <row r="680" spans="1:20" ht="18">
+    <row r="680" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A680" s="3" t="s">
         <v>1166</v>
       </c>
@@ -60285,7 +60287,7 @@
       </c>
       <c r="T680" s="6"/>
     </row>
-    <row r="681" spans="1:20" ht="18">
+    <row r="681" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A681" s="7" t="s">
         <v>1167</v>
       </c>
@@ -60343,7 +60345,7 @@
       </c>
       <c r="T681" s="6"/>
     </row>
-    <row r="682" spans="1:20" ht="18">
+    <row r="682" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A682" s="3" t="s">
         <v>1168</v>
       </c>
@@ -60401,7 +60403,7 @@
       </c>
       <c r="T682" s="6"/>
     </row>
-    <row r="683" spans="1:20" ht="18">
+    <row r="683" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A683" s="7" t="s">
         <v>1169</v>
       </c>
@@ -60459,7 +60461,7 @@
       </c>
       <c r="T683" s="6"/>
     </row>
-    <row r="684" spans="1:20" ht="18">
+    <row r="684" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A684" s="3" t="s">
         <v>1170</v>
       </c>
@@ -60517,7 +60519,7 @@
       </c>
       <c r="T684" s="6"/>
     </row>
-    <row r="685" spans="1:20" ht="18">
+    <row r="685" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A685" s="7" t="s">
         <v>1171</v>
       </c>
@@ -60575,7 +60577,7 @@
       </c>
       <c r="T685" s="6"/>
     </row>
-    <row r="686" spans="1:20" ht="18">
+    <row r="686" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A686" s="3" t="s">
         <v>1173</v>
       </c>
@@ -60633,7 +60635,7 @@
       </c>
       <c r="T686" s="6"/>
     </row>
-    <row r="687" spans="1:20" ht="18">
+    <row r="687" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A687" s="7" t="s">
         <v>1174</v>
       </c>
@@ -60691,7 +60693,7 @@
       </c>
       <c r="T687" s="6"/>
     </row>
-    <row r="688" spans="1:20" ht="18">
+    <row r="688" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A688" s="3" t="s">
         <v>1176</v>
       </c>
@@ -60749,7 +60751,7 @@
       </c>
       <c r="T688" s="6"/>
     </row>
-    <row r="689" spans="1:20" ht="18">
+    <row r="689" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A689" s="7" t="s">
         <v>1177</v>
       </c>
@@ -60807,7 +60809,7 @@
       </c>
       <c r="T689" s="6"/>
     </row>
-    <row r="690" spans="1:20" ht="18">
+    <row r="690" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A690" s="3" t="s">
         <v>1179</v>
       </c>
@@ -60865,7 +60867,7 @@
       </c>
       <c r="T690" s="6"/>
     </row>
-    <row r="691" spans="1:20" ht="18">
+    <row r="691" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A691" s="7" t="s">
         <v>1180</v>
       </c>
@@ -60923,7 +60925,7 @@
       </c>
       <c r="T691" s="6"/>
     </row>
-    <row r="692" spans="1:20" ht="18">
+    <row r="692" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A692" s="3" t="s">
         <v>1181</v>
       </c>
@@ -60981,7 +60983,7 @@
       </c>
       <c r="T692" s="6"/>
     </row>
-    <row r="693" spans="1:20" ht="18">
+    <row r="693" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A693" s="7" t="s">
         <v>1182</v>
       </c>
@@ -61039,7 +61041,7 @@
       </c>
       <c r="T693" s="6"/>
     </row>
-    <row r="694" spans="1:20" ht="18">
+    <row r="694" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A694" s="3" t="s">
         <v>1183</v>
       </c>
@@ -61097,7 +61099,7 @@
       </c>
       <c r="T694" s="6"/>
     </row>
-    <row r="695" spans="1:20" ht="18">
+    <row r="695" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A695" s="7" t="s">
         <v>1184</v>
       </c>
@@ -61155,7 +61157,7 @@
       </c>
       <c r="T695" s="6"/>
     </row>
-    <row r="696" spans="1:20" ht="18">
+    <row r="696" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A696" s="3" t="s">
         <v>1185</v>
       </c>
@@ -61213,7 +61215,7 @@
       </c>
       <c r="T696" s="6"/>
     </row>
-    <row r="697" spans="1:20" ht="18">
+    <row r="697" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A697" s="7" t="s">
         <v>1186</v>
       </c>
@@ -61271,7 +61273,7 @@
       </c>
       <c r="T697" s="6"/>
     </row>
-    <row r="698" spans="1:20" ht="18">
+    <row r="698" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A698" s="17" t="s">
         <v>1187</v>
       </c>
@@ -61329,7 +61331,7 @@
       </c>
       <c r="T698" s="20"/>
     </row>
-    <row r="699" spans="1:20" ht="0" hidden="1" customHeight="1"/>
+    <row r="699" spans="1:20" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -61355,7 +61357,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.85546875" customWidth="1"/>
     <col min="2" max="2" width="43.42578125" customWidth="1"/>
@@ -61364,15 +61366,15 @@
     <col min="5" max="5" width="255" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="127.5" customHeight="1">
-      <c r="A1" s="21" t="s">
+    <row r="1" spans="1:3" ht="127.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="25" t="s">
         <v>1189</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-    </row>
-    <row r="2" spans="1:3" ht="17.100000000000001" customHeight="1"/>
-    <row r="3" spans="1:3" ht="18">
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+    </row>
+    <row r="2" spans="1:3" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>1190</v>
       </c>
@@ -61383,8 +61385,8 @@
         <v>1191</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="18">
-      <c r="A4" s="22" t="s">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="27" t="s">
         <v>1192</v>
       </c>
       <c r="B4" s="13" t="s">
@@ -61394,8 +61396,8 @@
         <v>1193</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="18">
-      <c r="A5" s="23"/>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="28"/>
       <c r="B5" s="13" t="s">
         <v>32</v>
       </c>
@@ -61403,8 +61405,8 @@
         <v>1194</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="18">
-      <c r="A6" s="23"/>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="28"/>
       <c r="B6" s="13" t="s">
         <v>362</v>
       </c>
@@ -61412,8 +61414,8 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="18">
-      <c r="A7" s="24"/>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="29"/>
       <c r="B7" s="13" t="s">
         <v>1196</v>
       </c>
@@ -61421,8 +61423,8 @@
         <v>1197</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="18">
-      <c r="A8" s="25" t="s">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="30" t="s">
         <v>1198</v>
       </c>
       <c r="B8" s="13" t="s">
@@ -61432,8 +61434,8 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="18">
-      <c r="A9" s="26"/>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="31"/>
       <c r="B9" s="13" t="s">
         <v>1198</v>
       </c>
@@ -61441,8 +61443,8 @@
         <v>1201</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="18">
-      <c r="A10" s="27"/>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="32"/>
       <c r="B10" s="15" t="s">
         <v>1202</v>
       </c>
@@ -61450,8 +61452,8 @@
         <v>1203</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="146.44999999999999" customHeight="1"/>
-    <row r="12" spans="1:3" ht="99.6" customHeight="1"/>
+    <row r="11" spans="1:3" ht="146.44999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="1:3" ht="99.6" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:C1"/>
@@ -61467,124 +61469,120 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B848CA76-6293-490C-949E-20759110FBC9}">
   <dimension ref="A3:H8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="8" width="9.5703125" style="31" customWidth="1"/>
+    <col min="2" max="8" width="9.5703125" style="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:7">
-      <c r="A3" s="28" t="s">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="21" t="s">
         <v>1204</v>
       </c>
-      <c r="B3" s="30" t="s">
+      <c r="B3" s="23" t="s">
         <v>1205</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="28" t="s">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="21" t="s">
         <v>1206</v>
       </c>
-      <c r="B4" s="31" t="s">
+      <c r="B4" s="24" t="s">
         <v>745</v>
       </c>
-      <c r="C4" s="31" t="s">
+      <c r="C4" s="24" t="s">
         <v>451</v>
       </c>
-      <c r="D4" s="31" t="s">
+      <c r="D4" s="24" t="s">
         <v>375</v>
       </c>
-      <c r="E4" s="31" t="s">
+      <c r="E4" s="24" t="s">
         <v>345</v>
       </c>
-      <c r="F4" s="31" t="s">
+      <c r="F4" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="G4" s="31" t="s">
+      <c r="G4" s="24" t="s">
         <v>1207</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="29" t="s">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="B5" s="32"/>
-      <c r="C5" s="32">
+      <c r="C5" s="24">
         <v>56</v>
       </c>
-      <c r="D5" s="32">
+      <c r="D5" s="24">
         <v>3</v>
       </c>
-      <c r="E5" s="32"/>
-      <c r="F5" s="32">
+      <c r="F5" s="24">
         <v>11</v>
       </c>
-      <c r="G5" s="32">
+      <c r="G5" s="24">
         <v>70</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="29" t="s">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="B6" s="32"/>
-      <c r="C6" s="32">
+      <c r="C6" s="24">
         <v>74</v>
       </c>
-      <c r="D6" s="32">
+      <c r="D6" s="24">
         <v>35</v>
       </c>
-      <c r="E6" s="32">
+      <c r="E6" s="24">
         <v>10</v>
       </c>
-      <c r="F6" s="32">
+      <c r="F6" s="24">
         <v>143</v>
       </c>
-      <c r="G6" s="32">
+      <c r="G6" s="24">
         <v>262</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="29" t="s">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="22" t="s">
         <v>362</v>
       </c>
-      <c r="B7" s="32">
+      <c r="B7" s="24">
         <v>323</v>
       </c>
-      <c r="C7" s="32">
+      <c r="C7" s="24">
         <v>40</v>
       </c>
-      <c r="D7" s="32">
+      <c r="D7" s="24">
         <v>1</v>
       </c>
-      <c r="E7" s="32">
+      <c r="E7" s="24">
         <v>1</v>
       </c>
-      <c r="F7" s="32"/>
-      <c r="G7" s="32">
+      <c r="G7" s="24">
         <v>365</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="29" t="s">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="22" t="s">
         <v>1207</v>
       </c>
-      <c r="B8" s="32">
+      <c r="B8" s="24">
         <v>323</v>
       </c>
-      <c r="C8" s="32">
+      <c r="C8" s="24">
         <v>170</v>
       </c>
-      <c r="D8" s="32">
+      <c r="D8" s="24">
         <v>39</v>
       </c>
-      <c r="E8" s="32">
+      <c r="E8" s="24">
         <v>11</v>
       </c>
-      <c r="F8" s="32">
+      <c r="F8" s="24">
         <v>154</v>
       </c>
-      <c r="G8" s="32">
+      <c r="G8" s="24">
         <v>697</v>
       </c>
     </row>
@@ -61594,14 +61592,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="45f0512c-3bd3-4a39-812e-746c3981abe0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="1329bb7b-24e0-463f-964f-81d6e0aa7226" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -61800,22 +61796,50 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="45f0512c-3bd3-4a39-812e-746c3981abe0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="1329bb7b-24e0-463f-964f-81d6e0aa7226" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6D0DE980-3E87-4E29-B084-C8155323E80C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3D8B69F7-E39C-4B5E-8CD7-9797E1F7B7E1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F22A51CA-1D92-4A37-9711-A63B78BB3259}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F22A51CA-1D92-4A37-9711-A63B78BB3259}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="45f0512c-3bd3-4a39-812e-746c3981abe0"/>
+    <ds:schemaRef ds:uri="1329bb7b-24e0-463f-964f-81d6e0aa7226"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3D8B69F7-E39C-4B5E-8CD7-9797E1F7B7E1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6D0DE980-3E87-4E29-B084-C8155323E80C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="45f0512c-3bd3-4a39-812e-746c3981abe0"/>
+    <ds:schemaRef ds:uri="1329bb7b-24e0-463f-964f-81d6e0aa7226"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/files/upload/excel/20260817_ID-IBM_ID-_POU_Unreturned.xlsx
+++ b/files/upload/excel/20260817_ID-IBM_ID-_POU_Unreturned.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\IBM\TEST-PYTHON\DEVELOPMENT\Development_v1.0\develop-lenovo-app\files\upload\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ibm-my.sharepoint.com/personal/miftah_choiri_ibm_com/Documents/IBM💼/PROJECTS🎯/OPPORTUNITY/LENOVO-REPORT/lenovo-apps/PoU unreturn/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A3059B7-D920-4A04-B8EC-43D3D4F14287}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="11_EB59AEE8F97DB29FF53E5B7B715A219348456A3E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A7844FD6-5348-49AC-A071-2CA9B89FB4CF}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1950" windowWidth="10110" windowHeight="15885" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -20854,7 +20854,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T699"/>
+  <dimension ref="A1:T698"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="20" width="25.7109375" customWidth="1"/>
@@ -61270,7 +61270,7 @@
       </c>
       <c r="T697" s="6"/>
     </row>
-    <row r="698" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:20" ht="59.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A698" s="17" t="s">
         <v>1186</v>
       </c>
@@ -61328,7 +61328,6 @@
       </c>
       <c r="T698" s="20"/>
     </row>
-    <row r="699" spans="1:20" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -61589,14 +61588,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="45f0512c-3bd3-4a39-812e-746c3981abe0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="1329bb7b-24e0-463f-964f-81d6e0aa7226" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -61795,21 +61792,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="45f0512c-3bd3-4a39-812e-746c3981abe0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="1329bb7b-24e0-463f-964f-81d6e0aa7226" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6D0DE980-3E87-4E29-B084-C8155323E80C}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3D8B69F7-E39C-4B5E-8CD7-9797E1F7B7E1}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="45f0512c-3bd3-4a39-812e-746c3981abe0"/>
-    <ds:schemaRef ds:uri="1329bb7b-24e0-463f-964f-81d6e0aa7226"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -61834,9 +61830,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3D8B69F7-E39C-4B5E-8CD7-9797E1F7B7E1}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6D0DE980-3E87-4E29-B084-C8155323E80C}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="45f0512c-3bd3-4a39-812e-746c3981abe0"/>
+    <ds:schemaRef ds:uri="1329bb7b-24e0-463f-964f-81d6e0aa7226"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>